--- a/tsmc/dist/20261025_台積電模型_v0.3.1.xlsx
+++ b/tsmc/dist/20261025_台積電模型_v0.3.1.xlsx
@@ -90,13 +90,29 @@
     <definedName function="false" hidden="false" name="fx_lo" vbProcedure="false">In!$D$77</definedName>
     <definedName function="false" hidden="false" name="g26_guid" vbProcedure="false">In!$E$101</definedName>
     <definedName function="false" hidden="false" name="g29_amd" vbProcedure="false">In!$E$24</definedName>
+    <definedName function="false" hidden="false" name="g29_amd_hi" vbProcedure="false">In!$F$24</definedName>
+    <definedName function="false" hidden="false" name="g29_amd_lo" vbProcedure="false">In!$D$24</definedName>
     <definedName function="false" hidden="false" name="g29_bw" vbProcedure="false">In!$E$8</definedName>
+    <definedName function="false" hidden="false" name="g29_bw_hi" vbProcedure="false">In!$F$8</definedName>
+    <definedName function="false" hidden="false" name="g29_bw_lo" vbProcedure="false">In!$D$8</definedName>
     <definedName function="false" hidden="false" name="g29_hp" vbProcedure="false">In!$E$20</definedName>
+    <definedName function="false" hidden="false" name="g29_hp_hi" vbProcedure="false">In!$F$20</definedName>
+    <definedName function="false" hidden="false" name="g29_hp_lo" vbProcedure="false">In!$D$20</definedName>
     <definedName function="false" hidden="false" name="g29_oth" vbProcedure="false">In!$E$36</definedName>
+    <definedName function="false" hidden="false" name="g29_oth_hi" vbProcedure="false">In!$F$36</definedName>
+    <definedName function="false" hidden="false" name="g29_oth_lo" vbProcedure="false">In!$D$36</definedName>
     <definedName function="false" hidden="false" name="g29_rb" vbProcedure="false">In!$E$12</definedName>
+    <definedName function="false" hidden="false" name="g29_rb_hi" vbProcedure="false">In!$F$12</definedName>
+    <definedName function="false" hidden="false" name="g29_rb_lo" vbProcedure="false">In!$D$12</definedName>
     <definedName function="false" hidden="false" name="g29_ru" vbProcedure="false">In!$E$16</definedName>
+    <definedName function="false" hidden="false" name="g29_ru_hi" vbProcedure="false">In!$F$16</definedName>
+    <definedName function="false" hidden="false" name="g29_ru_lo" vbProcedure="false">In!$D$16</definedName>
     <definedName function="false" hidden="false" name="g29_tpu" vbProcedure="false">In!$E$28</definedName>
+    <definedName function="false" hidden="false" name="g29_tpu_hi" vbProcedure="false">In!$F$28</definedName>
+    <definedName function="false" hidden="false" name="g29_tpu_lo" vbProcedure="false">In!$D$28</definedName>
     <definedName function="false" hidden="false" name="g29_trn" vbProcedure="false">In!$E$32</definedName>
+    <definedName function="false" hidden="false" name="g29_trn_hi" vbProcedure="false">In!$F$32</definedName>
+    <definedName function="false" hidden="false" name="g29_trn_lo" vbProcedure="false">In!$D$32</definedName>
     <definedName function="false" hidden="false" name="gm26" vbProcedure="false">In!$E$119</definedName>
     <definedName function="false" hidden="false" name="gm26_1q" vbProcedure="false">In!$E$88</definedName>
     <definedName function="false" hidden="false" name="gm26_2q" vbProcedure="false">In!$E$89</definedName>
@@ -255,7 +271,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1294" uniqueCount="845">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1302" uniqueCount="846">
   <si>
     <r>
       <rPr>
@@ -5345,6 +5361,65 @@
   </si>
   <si>
     <t xml:space="preserve">Assumed</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Siliconomics v0.2 SIF_g29_bw</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（單一來源；</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2029 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">無平台別顆數預測，區間 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">±10pt</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">u_rb_26</t>
@@ -34327,19 +34402,28 @@
       <c r="C8" s="0" t="s">
         <v>42</v>
       </c>
+      <c r="D8" s="7" t="n">
+        <v>-0.7</v>
+      </c>
       <c r="E8" s="7" t="n">
         <v>-0.5</v>
       </c>
+      <c r="F8" s="7" t="n">
+        <v>-0.3</v>
+      </c>
       <c r="G8" s="8" t="s">
         <v>43</v>
       </c>
+      <c r="H8" s="8" t="s">
+        <v>44</v>
+      </c>
     </row>
     <row r="9" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="0" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B9" s="0" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C9" s="4" t="s">
         <v>32</v>
@@ -34351,15 +34435,15 @@
         <v>33</v>
       </c>
       <c r="H9" s="8" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="0" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B10" s="0" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C10" s="4" t="s">
         <v>32</v>
@@ -34376,10 +34460,10 @@
     </row>
     <row r="11" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="0" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B11" s="0" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C11" s="4" t="s">
         <v>32</v>
@@ -34396,27 +34480,36 @@
     </row>
     <row r="12" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="0" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B12" s="0" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C12" s="0" t="s">
         <v>42</v>
       </c>
+      <c r="D12" s="7" t="n">
+        <v>0.05</v>
+      </c>
       <c r="E12" s="7" t="n">
         <v>0.15</v>
       </c>
+      <c r="F12" s="7" t="n">
+        <v>0.25</v>
+      </c>
       <c r="G12" s="8" t="s">
         <v>43</v>
       </c>
+      <c r="H12" s="4" t="s">
+        <v>37</v>
+      </c>
     </row>
     <row r="13" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="0" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B13" s="0" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C13" s="4" t="s">
         <v>32</v>
@@ -34428,15 +34521,15 @@
         <v>43</v>
       </c>
       <c r="H13" s="8" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="0" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B14" s="0" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C14" s="4" t="s">
         <v>32</v>
@@ -34453,10 +34546,10 @@
     </row>
     <row r="15" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="0" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B15" s="0" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C15" s="4" t="s">
         <v>32</v>
@@ -34473,27 +34566,36 @@
     </row>
     <row r="16" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="0" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B16" s="0" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C16" s="0" t="s">
         <v>42</v>
       </c>
+      <c r="D16" s="7" t="n">
+        <v>0.05</v>
+      </c>
       <c r="E16" s="7" t="n">
         <v>0.15</v>
       </c>
+      <c r="F16" s="7" t="n">
+        <v>0.25</v>
+      </c>
       <c r="G16" s="8" t="s">
         <v>43</v>
       </c>
+      <c r="H16" s="4" t="s">
+        <v>37</v>
+      </c>
     </row>
     <row r="17" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="0" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B17" s="0" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C17" s="4" t="s">
         <v>32</v>
@@ -34505,15 +34607,15 @@
         <v>33</v>
       </c>
       <c r="H17" s="8" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="0" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B18" s="0" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C18" s="4" t="s">
         <v>32</v>
@@ -34530,10 +34632,10 @@
     </row>
     <row r="19" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="0" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B19" s="0" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C19" s="4" t="s">
         <v>32</v>
@@ -34550,27 +34652,36 @@
     </row>
     <row r="20" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="0" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B20" s="0" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C20" s="0" t="s">
         <v>42</v>
       </c>
+      <c r="D20" s="7" t="n">
+        <v>0</v>
+      </c>
       <c r="E20" s="7" t="n">
         <v>0</v>
       </c>
+      <c r="F20" s="7" t="n">
+        <v>0</v>
+      </c>
       <c r="G20" s="8" t="s">
         <v>43</v>
       </c>
+      <c r="H20" s="4" t="s">
+        <v>37</v>
+      </c>
     </row>
     <row r="21" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="0" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B21" s="0" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C21" s="4" t="s">
         <v>32</v>
@@ -34579,18 +34690,18 @@
         <v>0.75</v>
       </c>
       <c r="G21" s="8" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H21" s="8" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="0" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B22" s="0" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C22" s="4" t="s">
         <v>32</v>
@@ -34599,7 +34710,7 @@
         <v>1.5</v>
       </c>
       <c r="G22" s="8" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H22" s="4" t="s">
         <v>37</v>
@@ -34607,10 +34718,10 @@
     </row>
     <row r="23" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="0" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B23" s="0" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C23" s="4" t="s">
         <v>32</v>
@@ -34619,7 +34730,7 @@
         <v>2</v>
       </c>
       <c r="G23" s="8" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H23" s="4" t="s">
         <v>37</v>
@@ -34627,27 +34738,36 @@
     </row>
     <row r="24" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="0" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B24" s="0" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C24" s="0" t="s">
         <v>42</v>
       </c>
+      <c r="D24" s="7" t="n">
+        <v>0.05</v>
+      </c>
       <c r="E24" s="7" t="n">
         <v>0.15</v>
       </c>
+      <c r="F24" s="7" t="n">
+        <v>0.25</v>
+      </c>
       <c r="G24" s="8" t="s">
         <v>43</v>
       </c>
+      <c r="H24" s="4" t="s">
+        <v>37</v>
+      </c>
     </row>
     <row r="25" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="0" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B25" s="0" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C25" s="4" t="s">
         <v>32</v>
@@ -34659,15 +34779,15 @@
         <v>33</v>
       </c>
       <c r="H25" s="8" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="0" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B26" s="0" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C26" s="4" t="s">
         <v>32</v>
@@ -34684,10 +34804,10 @@
     </row>
     <row r="27" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="0" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B27" s="0" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C27" s="4" t="s">
         <v>32</v>
@@ -34704,27 +34824,36 @@
     </row>
     <row r="28" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="0" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B28" s="0" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C28" s="0" t="s">
         <v>42</v>
       </c>
+      <c r="D28" s="7" t="n">
+        <v>0.05</v>
+      </c>
       <c r="E28" s="7" t="n">
         <v>0.15</v>
       </c>
+      <c r="F28" s="7" t="n">
+        <v>0.25</v>
+      </c>
       <c r="G28" s="8" t="s">
         <v>43</v>
       </c>
+      <c r="H28" s="4" t="s">
+        <v>37</v>
+      </c>
     </row>
     <row r="29" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="0" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B29" s="0" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C29" s="4" t="s">
         <v>32</v>
@@ -34736,15 +34865,15 @@
         <v>43</v>
       </c>
       <c r="H29" s="8" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="0" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B30" s="0" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C30" s="4" t="s">
         <v>32</v>
@@ -34761,10 +34890,10 @@
     </row>
     <row r="31" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="0" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B31" s="0" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C31" s="4" t="s">
         <v>32</v>
@@ -34781,27 +34910,36 @@
     </row>
     <row r="32" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="0" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B32" s="0" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C32" s="0" t="s">
         <v>42</v>
       </c>
+      <c r="D32" s="7" t="n">
+        <v>0.05</v>
+      </c>
       <c r="E32" s="7" t="n">
         <v>0.15</v>
       </c>
+      <c r="F32" s="7" t="n">
+        <v>0.25</v>
+      </c>
       <c r="G32" s="8" t="s">
         <v>43</v>
       </c>
+      <c r="H32" s="4" t="s">
+        <v>37</v>
+      </c>
     </row>
     <row r="33" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="0" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C33" s="4" t="s">
         <v>32</v>
@@ -34810,18 +34948,18 @@
         <v>1</v>
       </c>
       <c r="G33" s="8" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="H33" s="8" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="0" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C34" s="4" t="s">
         <v>32</v>
@@ -34830,7 +34968,7 @@
         <v>4.5</v>
       </c>
       <c r="G34" s="8" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="H34" s="4" t="s">
         <v>37</v>
@@ -34838,10 +34976,10 @@
     </row>
     <row r="35" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="0" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C35" s="4" t="s">
         <v>32</v>
@@ -34850,7 +34988,7 @@
         <v>5</v>
       </c>
       <c r="G35" s="8" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="H35" s="4" t="s">
         <v>37</v>
@@ -34858,30 +34996,39 @@
     </row>
     <row r="36" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="0" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C36" s="0" t="s">
         <v>42</v>
       </c>
+      <c r="D36" s="7" t="n">
+        <v>0.05</v>
+      </c>
       <c r="E36" s="7" t="n">
         <v>0.15</v>
       </c>
+      <c r="F36" s="7" t="n">
+        <v>0.25</v>
+      </c>
       <c r="G36" s="8" t="s">
         <v>43</v>
       </c>
+      <c r="H36" s="4" t="s">
+        <v>37</v>
+      </c>
     </row>
     <row r="37" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="0" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C37" s="0" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="E37" s="7" t="n">
         <v>1</v>
@@ -34890,18 +35037,18 @@
         <v>43</v>
       </c>
       <c r="H37" s="8" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="0" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C38" s="0" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="E38" s="7" t="n">
         <v>1</v>
@@ -34912,13 +35059,13 @@
     </row>
     <row r="39" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="0" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C39" s="0" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="E39" s="7" t="n">
         <v>0.8</v>
@@ -34929,13 +35076,13 @@
     </row>
     <row r="40" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="0" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C40" s="0" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="E40" s="7" t="n">
         <v>0.85</v>
@@ -34946,13 +35093,13 @@
     </row>
     <row r="41" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="0" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C41" s="0" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="E41" s="7" t="n">
         <v>0.6</v>
@@ -34963,13 +35110,13 @@
     </row>
     <row r="42" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="0" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C42" s="0" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="E42" s="7" t="n">
         <v>0.6</v>
@@ -34980,18 +35127,18 @@
     </row>
     <row r="43" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="6" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="0" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B44" s="0" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C44" s="4" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D44" s="7" t="n">
         <v>11.2</v>
@@ -35003,21 +35150,21 @@
         <v>16.8</v>
       </c>
       <c r="G44" s="8" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="H44" s="4" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="0" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B45" s="0" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C45" s="0" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D45" s="7" t="n">
         <v>1.84</v>
@@ -35029,7 +35176,7 @@
         <v>2.76</v>
       </c>
       <c r="G45" s="8" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="H45" s="4" t="s">
         <v>37</v>
@@ -35037,13 +35184,13 @@
     </row>
     <row r="46" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="0" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B46" s="0" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C46" s="4" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D46" s="7" t="n">
         <v>6.4</v>
@@ -35055,21 +35202,21 @@
         <v>9.6</v>
       </c>
       <c r="G46" s="8" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="H46" s="8" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="0" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B47" s="0" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C47" s="0" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D47" s="7" t="n">
         <v>2.24</v>
@@ -35081,7 +35228,7 @@
         <v>3.36</v>
       </c>
       <c r="G47" s="8" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="H47" s="4" t="s">
         <v>37</v>
@@ -35089,13 +35236,13 @@
     </row>
     <row r="48" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="0" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B48" s="0" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C48" s="4" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D48" s="7" t="n">
         <v>3.2</v>
@@ -35110,18 +35257,18 @@
         <v>43</v>
       </c>
       <c r="H48" s="8" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="0" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B49" s="0" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C49" s="0" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D49" s="7" t="n">
         <v>4.8</v>
@@ -35141,13 +35288,13 @@
     </row>
     <row r="50" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="0" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B50" s="0" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C50" s="4" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D50" s="7" t="n">
         <v>23.2</v>
@@ -35159,21 +35306,21 @@
         <v>34.8</v>
       </c>
       <c r="G50" s="8" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="H50" s="8" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="0" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B51" s="0" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C51" s="0" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D51" s="7" t="n">
         <v>0.88</v>
@@ -35185,7 +35332,7 @@
         <v>1.32</v>
       </c>
       <c r="G51" s="8" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="H51" s="4" t="s">
         <v>37</v>
@@ -35193,13 +35340,13 @@
     </row>
     <row r="52" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="0" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B52" s="0" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C52" s="4" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D52" s="7" t="n">
         <v>6.8</v>
@@ -35211,21 +35358,21 @@
         <v>10.2</v>
       </c>
       <c r="G52" s="8" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="H52" s="8" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="0" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B53" s="0" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C53" s="0" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D53" s="7" t="n">
         <v>1.6</v>
@@ -35237,7 +35384,7 @@
         <v>2.4</v>
       </c>
       <c r="G53" s="8" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="H53" s="4" t="s">
         <v>37</v>
@@ -35245,13 +35392,13 @@
     </row>
     <row r="54" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="0" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B54" s="0" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C54" s="4" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D54" s="7" t="n">
         <v>4.8</v>
@@ -35266,18 +35413,18 @@
         <v>43</v>
       </c>
       <c r="H54" s="8" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="0" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B55" s="0" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C55" s="0" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D55" s="7" t="n">
         <v>2.4</v>
@@ -35297,13 +35444,13 @@
     </row>
     <row r="56" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="0" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B56" s="0" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C56" s="4" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D56" s="7" t="n">
         <v>22.4</v>
@@ -35315,21 +35462,21 @@
         <v>33.6</v>
       </c>
       <c r="G56" s="8" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="H56" s="8" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="0" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B57" s="0" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C57" s="0" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D57" s="7" t="n">
         <v>1.2</v>
@@ -35341,7 +35488,7 @@
         <v>1.8</v>
       </c>
       <c r="G57" s="8" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="H57" s="4" t="s">
         <v>37</v>
@@ -35349,13 +35496,13 @@
     </row>
     <row r="58" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="0" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B58" s="0" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C58" s="4" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D58" s="7" t="n">
         <v>19.2</v>
@@ -35370,18 +35517,18 @@
         <v>43</v>
       </c>
       <c r="H58" s="8" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="0" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B59" s="0" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C59" s="0" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D59" s="7" t="n">
         <v>1.44</v>
@@ -35401,13 +35548,13 @@
     </row>
     <row r="60" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="0" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B60" s="0" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C60" s="4" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D60" s="7" t="n">
         <v>24</v>
@@ -35419,21 +35566,21 @@
         <v>36</v>
       </c>
       <c r="G60" s="8" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="H60" s="8" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="0" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B61" s="0" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C61" s="0" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D61" s="7" t="n">
         <v>0.96</v>
@@ -35445,7 +35592,7 @@
         <v>1.44</v>
       </c>
       <c r="G61" s="8" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="H61" s="4" t="s">
         <v>37</v>
@@ -35453,13 +35600,13 @@
     </row>
     <row r="62" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="0" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B62" s="0" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C62" s="4" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D62" s="7" t="n">
         <v>16</v>
@@ -35476,13 +35623,13 @@
     </row>
     <row r="63" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="0" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B63" s="0" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C63" s="0" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D63" s="7" t="n">
         <v>0.96</v>
@@ -35502,13 +35649,13 @@
     </row>
     <row r="64" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="0" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B64" s="4" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C64" s="4" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="E64" s="7" t="n">
         <v>150</v>
@@ -35517,15 +35664,15 @@
         <v>43</v>
       </c>
       <c r="H64" s="8" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="0" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B65" s="4" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C65" s="0" t="s">
         <v>42</v>
@@ -35539,18 +35686,18 @@
     </row>
     <row r="66" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="6" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="0" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B67" s="0" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C67" s="4" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="E67" s="7" t="n">
         <v>77.5</v>
@@ -35559,18 +35706,18 @@
         <v>33</v>
       </c>
       <c r="H67" s="8" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="0" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B68" s="0" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C68" s="4" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="E68" s="7" t="n">
         <v>130</v>
@@ -35579,18 +35726,18 @@
         <v>33</v>
       </c>
       <c r="H68" s="8" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="0" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B69" s="0" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C69" s="4" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="E69" s="7" t="n">
         <v>200</v>
@@ -35599,18 +35746,18 @@
         <v>33</v>
       </c>
       <c r="H69" s="8" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="0" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B70" s="0" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C70" s="4" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="E70" s="7" t="n">
         <v>260</v>
@@ -35619,18 +35766,18 @@
         <v>33</v>
       </c>
       <c r="H70" s="8" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="0" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B71" s="0" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C71" s="4" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="E71" s="7" t="n">
         <v>320</v>
@@ -35644,10 +35791,10 @@
     </row>
     <row r="72" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="0" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B72" s="4" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C72" s="0" t="s">
         <v>42</v>
@@ -35665,18 +35812,18 @@
         <v>43</v>
       </c>
       <c r="H72" s="4" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="0" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B73" s="0" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C73" s="4" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="E73" s="7" t="n">
         <v>1394</v>
@@ -35685,18 +35832,18 @@
         <v>33</v>
       </c>
       <c r="H73" s="8" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="0" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B74" s="0" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="C74" s="4" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="E74" s="7" t="n">
         <v>2509</v>
@@ -35705,15 +35852,15 @@
         <v>33</v>
       </c>
       <c r="H74" s="8" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="0" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B75" s="0" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C75" s="0" t="s">
         <v>42</v>
@@ -35722,26 +35869,26 @@
         <v>0.21</v>
       </c>
       <c r="G75" s="8" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="H75" s="8" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="0" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B77" s="4" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="C77" s="0" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="D77" s="7" t="n">
         <v>30</v>
@@ -35756,98 +35903,98 @@
         <v>43</v>
       </c>
       <c r="H77" s="8" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="0" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B78" s="4" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C78" s="0" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E78" s="7" t="n">
         <v>122.43</v>
       </c>
       <c r="G78" s="8" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H78" s="4" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="0" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B79" s="4" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="C79" s="0" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E79" s="7" t="n">
         <v>35.9</v>
       </c>
       <c r="G79" s="8" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H79" s="4" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="0" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B80" s="4" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C80" s="0" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E80" s="7" t="n">
         <v>40.2</v>
       </c>
       <c r="G80" s="8" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H80" s="4" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="0" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B81" s="4" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C81" s="0" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E81" s="7" t="n">
         <v>46.72</v>
       </c>
       <c r="G81" s="8" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H81" s="4" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="0" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B82" s="4" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="C82" s="0" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="D82" s="7" t="n">
         <v>52.3</v>
@@ -35862,18 +36009,18 @@
         <v>33</v>
       </c>
       <c r="H82" s="4" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="0" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B83" s="0" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="C83" s="0" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="E83" s="7" t="n">
         <v>31.8</v>
@@ -35882,78 +36029,78 @@
         <v>33</v>
       </c>
       <c r="H83" s="4" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="0" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B84" s="4" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C84" s="0" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="E84" s="7" t="n">
         <v>1134.1</v>
       </c>
       <c r="G84" s="8" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H84" s="4" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="0" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B85" s="4" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="C85" s="0" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="E85" s="7" t="n">
         <v>1270.38</v>
       </c>
       <c r="G85" s="8" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H85" s="4" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="0" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B86" s="4" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C86" s="0" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="E86" s="7" t="n">
         <v>1494.24</v>
       </c>
       <c r="G86" s="8" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H86" s="4" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="0" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B87" s="4" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C87" s="0" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="D87" s="0" t="n">
         <f aca="false">rev26_4q_lo*fx26_4q</f>
@@ -35968,15 +36115,15 @@
         <v>1726.74</v>
       </c>
       <c r="G87" s="0" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="0" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B88" s="4" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="C88" s="0" t="s">
         <v>42</v>
@@ -35985,18 +36132,18 @@
         <v>0.662</v>
       </c>
       <c r="G88" s="8" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H88" s="4" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="0" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B89" s="4" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C89" s="0" t="s">
         <v>42</v>
@@ -36005,18 +36152,18 @@
         <v>0.677</v>
       </c>
       <c r="G89" s="8" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H89" s="4" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="0" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B90" s="4" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C90" s="0" t="s">
         <v>42</v>
@@ -36025,18 +36172,18 @@
         <v>0.664</v>
       </c>
       <c r="G90" s="8" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H90" s="4" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="0" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B91" s="4" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="C91" s="0" t="s">
         <v>42</v>
@@ -36054,15 +36201,15 @@
         <v>33</v>
       </c>
       <c r="H91" s="4" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="0" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B92" s="4" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="C92" s="0" t="s">
         <v>42</v>
@@ -36071,18 +36218,18 @@
         <v>0.581</v>
       </c>
       <c r="G92" s="8" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H92" s="4" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="0" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B93" s="4" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C93" s="0" t="s">
         <v>42</v>
@@ -36091,18 +36238,18 @@
         <v>0.603</v>
       </c>
       <c r="G93" s="8" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H93" s="4" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="0" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B94" s="4" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C94" s="0" t="s">
         <v>42</v>
@@ -36111,18 +36258,18 @@
         <v>0.587</v>
       </c>
       <c r="G94" s="8" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H94" s="4" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="0" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B95" s="4" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="C95" s="0" t="s">
         <v>42</v>
@@ -36140,96 +36287,96 @@
         <v>33</v>
       </c>
       <c r="H95" s="4" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="0" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B96" s="4" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="C96" s="0" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="E96" s="7" t="n">
         <v>572.48</v>
       </c>
       <c r="G96" s="8" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H96" s="4" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="0" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B97" s="4" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="C97" s="0" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="E97" s="7" t="n">
         <v>706.56</v>
       </c>
       <c r="G97" s="8" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H97" s="4" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="0" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B98" s="4" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C98" s="0" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="E98" s="7" t="n">
         <v>763.06</v>
       </c>
       <c r="G98" s="8" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H98" s="4" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="0" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B99" s="0" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="C99" s="0" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="E99" s="0" t="n">
         <f aca="false">22.08+27.25+29.43</f>
         <v>78.76</v>
       </c>
       <c r="G99" s="0" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H99" s="4" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A100" s="0" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B100" s="0" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="C100" s="0" t="s">
         <v>42</v>
@@ -36238,18 +36385,18 @@
         <v>0.68</v>
       </c>
       <c r="G100" s="8" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H100" s="4" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A101" s="0" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B101" s="4" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="C101" s="0" t="s">
         <v>42</v>
@@ -36261,18 +36408,18 @@
         <v>33</v>
       </c>
       <c r="H101" s="4" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
     </row>
     <row r="102" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A102" s="0" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B102" s="4" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="C102" s="0" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="D102" s="0" t="n">
         <f aca="false">rev26_1q+rev26_2q+rev26_3q+rev26_4q_lo</f>
@@ -36287,57 +36434,57 @@
         <v>177.12</v>
       </c>
       <c r="G102" s="0" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="H102" s="0" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="103" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A103" s="0" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B103" s="4" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="C103" s="0" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="E103" s="0" t="n">
         <f aca="false">ntd26_1q+ntd26_2q+ntd26_3q+ntd26_4q</f>
         <v>5593.66</v>
       </c>
       <c r="G103" s="0" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="104" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A104" s="0" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B104" s="0" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="C104" s="0" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="E104" s="0" t="n">
         <f aca="false">ntd26/rev26</f>
         <v>31.7605042016807</v>
       </c>
       <c r="G104" s="0" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="H104" s="4" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="105" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A105" s="0" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B105" s="4" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="C105" s="0" t="s">
         <v>42</v>
@@ -36355,15 +36502,15 @@
         <v>43</v>
       </c>
       <c r="H105" s="4" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="106" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A106" s="0" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B106" s="0" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="C106" s="0" t="s">
         <v>42</v>
@@ -36372,18 +36519,18 @@
         <v>0.12</v>
       </c>
       <c r="G106" s="8" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="H106" s="8" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="107" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A107" s="0" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B107" s="0" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="C107" s="0" t="s">
         <v>42</v>
@@ -36392,7 +36539,7 @@
         <v>0.08</v>
       </c>
       <c r="G107" s="8" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="H107" s="8" t="s">
         <v>43</v>
@@ -36400,10 +36547,10 @@
     </row>
     <row r="108" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A108" s="0" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B108" s="0" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="C108" s="0" t="s">
         <v>42</v>
@@ -36412,7 +36559,7 @@
         <v>0.05</v>
       </c>
       <c r="G108" s="8" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="H108" s="8" t="s">
         <v>43</v>
@@ -36420,10 +36567,10 @@
     </row>
     <row r="109" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A109" s="0" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B109" s="4" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="C109" s="0" t="s">
         <v>42</v>
@@ -36435,15 +36582,15 @@
         <v>43</v>
       </c>
       <c r="H109" s="4" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="110" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A110" s="0" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B110" s="4" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="C110" s="0" t="s">
         <v>42</v>
@@ -36457,10 +36604,10 @@
     </row>
     <row r="111" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A111" s="0" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B111" s="4" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C111" s="0" t="s">
         <v>42</v>
@@ -36474,10 +36621,10 @@
     </row>
     <row r="112" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A112" s="0" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B112" s="4" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="C112" s="0" t="s">
         <v>42</v>
@@ -36491,10 +36638,10 @@
     </row>
     <row r="113" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A113" s="0" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B113" s="4" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C113" s="0" t="s">
         <v>42</v>
@@ -36508,10 +36655,10 @@
     </row>
     <row r="114" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A114" s="0" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B114" s="4" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="C114" s="0" t="s">
         <v>42</v>
@@ -36525,10 +36672,10 @@
     </row>
     <row r="115" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A115" s="0" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B115" s="4" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="C115" s="0" t="s">
         <v>42</v>
@@ -36542,10 +36689,10 @@
     </row>
     <row r="116" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A116" s="0" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B116" s="4" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="C116" s="0" t="s">
         <v>42</v>
@@ -36559,10 +36706,10 @@
     </row>
     <row r="117" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A117" s="0" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B117" s="4" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="C117" s="0" t="s">
         <v>42</v>
@@ -36576,15 +36723,15 @@
     </row>
     <row r="118" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A118" s="6" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="119" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A119" s="0" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B119" s="4" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="C119" s="0" t="s">
         <v>42</v>
@@ -36594,18 +36741,18 @@
         <v>0.665334900583875</v>
       </c>
       <c r="G119" s="0" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="H119" s="0" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="120" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A120" s="0" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B120" s="4" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="C120" s="0" t="s">
         <v>42</v>
@@ -36615,15 +36762,15 @@
         <v>0.58578115580854</v>
       </c>
       <c r="G120" s="0" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="121" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A121" s="0" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B121" s="4" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="C121" s="0" t="s">
         <v>42</v>
@@ -36633,39 +36780,39 @@
         <v>0.0795537447753351</v>
       </c>
       <c r="G121" s="0" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="H121" s="4" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="122" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A122" s="0" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B122" s="4" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="C122" s="0" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="E122" s="0" t="n">
         <f aca="false">(ni26_1q+ni26_2q+ni26_3q)/(ntd26_1q*opm26_1q+ntd26_2q*opm26_2q+ntd26_3q*opm26_3q)</f>
         <v>0.887071154896012</v>
       </c>
       <c r="G122" s="0" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="H122" s="0" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="123" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A123" s="0" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B123" s="4" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="C123" s="0" t="s">
         <v>42</v>
@@ -36674,18 +36821,18 @@
         <v>0.64</v>
       </c>
       <c r="G123" s="8" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="H123" s="8" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="124" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A124" s="0" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B124" s="4" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="C124" s="0" t="s">
         <v>42</v>
@@ -36694,15 +36841,15 @@
         <v>0.63</v>
       </c>
       <c r="G124" s="8" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="125" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A125" s="0" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B125" s="4" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="C125" s="0" t="s">
         <v>42</v>
@@ -36711,15 +36858,15 @@
         <v>0.62</v>
       </c>
       <c r="G125" s="8" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="126" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A126" s="0" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B126" s="4" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="C126" s="0" t="s">
         <v>42</v>
@@ -36728,15 +36875,15 @@
         <v>0.64</v>
       </c>
       <c r="G126" s="8" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="127" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A127" s="0" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B127" s="4" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="C127" s="0" t="s">
         <v>42</v>
@@ -36745,15 +36892,15 @@
         <v>0.58</v>
       </c>
       <c r="G127" s="8" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="128" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A128" s="0" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B128" s="4" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="C128" s="0" t="s">
         <v>42</v>
@@ -36762,15 +36909,15 @@
         <v>0.56</v>
       </c>
       <c r="G128" s="8" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="129" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A129" s="0" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B129" s="4" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="C129" s="0" t="s">
         <v>42</v>
@@ -36779,15 +36926,15 @@
         <v>0.64</v>
       </c>
       <c r="G129" s="8" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="130" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A130" s="0" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B130" s="4" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="C130" s="0" t="s">
         <v>42</v>
@@ -36796,15 +36943,15 @@
         <v>0.54</v>
       </c>
       <c r="G130" s="8" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="131" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A131" s="0" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="B131" s="4" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="C131" s="0" t="s">
         <v>42</v>
@@ -36813,15 +36960,15 @@
         <v>0.52</v>
       </c>
       <c r="G131" s="8" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="132" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A132" s="0" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B132" s="4" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="C132" s="0" t="s">
         <v>42</v>
@@ -36830,21 +36977,21 @@
         <v>0.075</v>
       </c>
       <c r="G132" s="8" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="H132" s="8" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
     <row r="133" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A133" s="0" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B133" s="4" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="C133" s="0" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="D133" s="9" t="n">
         <f aca="false">ni_op_underlying</f>
@@ -36859,61 +37006,61 @@
         <v>0.909166874667651</v>
       </c>
       <c r="G133" s="8" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="H133" s="4" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
     </row>
     <row r="134" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A134" s="0" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="B134" s="4" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="C134" s="4" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="E134" s="7" t="n">
         <v>25.93</v>
       </c>
       <c r="G134" s="8" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="H134" s="4" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
     </row>
     <row r="135" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A135" s="0" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B135" s="4" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="C135" s="0" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="E135" s="7" t="n">
         <v>2385</v>
       </c>
       <c r="G135" s="8" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H135" s="8" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="136" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A136" s="0" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B136" s="4" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="C136" s="0" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E136" s="7" t="n">
         <v>62</v>
@@ -36922,18 +37069,18 @@
         <v>33</v>
       </c>
       <c r="H136" s="4" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="137" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A137" s="0" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="B137" s="4" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C137" s="0" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E137" s="7" t="n">
         <v>77</v>
@@ -36942,18 +37089,18 @@
         <v>33</v>
       </c>
       <c r="H137" s="8" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="138" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A138" s="0" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="B138" s="4" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="C138" s="0" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E138" s="7" t="n">
         <v>90</v>
@@ -36962,18 +37109,18 @@
         <v>33</v>
       </c>
       <c r="H138" s="8" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="139" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A139" s="0" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="B139" s="4" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="C139" s="0" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E139" s="7" t="n">
         <v>95</v>
@@ -36984,13 +37131,13 @@
     </row>
     <row r="140" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A140" s="0" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="B140" s="0" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="C140" s="0" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="E140" s="7" t="n">
         <v>15</v>
@@ -36999,18 +37146,18 @@
         <v>33</v>
       </c>
       <c r="H140" s="4" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="141" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A141" s="0" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="B141" s="0" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="C141" s="0" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="E141" s="7" t="n">
         <v>20.5</v>
@@ -37019,18 +37166,18 @@
         <v>33</v>
       </c>
       <c r="H141" s="8" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="142" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A142" s="0" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="B142" s="0" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C142" s="0" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="E142" s="7" t="n">
         <v>32.7</v>
@@ -37039,18 +37186,18 @@
         <v>33</v>
       </c>
       <c r="H142" s="8" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="143" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A143" s="0" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="B143" s="4" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="C143" s="0" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E143" s="7" t="n">
         <v>229</v>
@@ -37059,18 +37206,18 @@
         <v>33</v>
       </c>
       <c r="H143" s="8" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="144" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A144" s="0" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="B144" s="4" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="C144" s="0" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="E144" s="7" t="n">
         <v>107.6</v>
@@ -37079,18 +37226,18 @@
         <v>33</v>
       </c>
       <c r="H144" s="8" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="145" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A145" s="0" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="B145" s="4" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="C145" s="0" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="E145" s="7" t="n">
         <v>142</v>
@@ -37099,15 +37246,15 @@
         <v>33</v>
       </c>
       <c r="H145" s="8" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="146" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A146" s="0" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="B146" s="0" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="C146" s="0" t="s">
         <v>42</v>
@@ -37116,18 +37263,18 @@
         <v>0.18</v>
       </c>
       <c r="G146" s="8" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H146" s="4" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="147" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A147" s="0" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="B147" s="0" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="C147" s="0" t="s">
         <v>42</v>
@@ -37136,18 +37283,18 @@
         <v>0.57</v>
       </c>
       <c r="G147" s="8" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H147" s="4" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="148" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A148" s="10" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="B148" s="11" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="C148" s="10" t="s">
         <v>42</v>
@@ -37161,15 +37308,15 @@
         <v>43</v>
       </c>
       <c r="H148" s="10" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="149" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A149" s="10" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="B149" s="11" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="C149" s="10" t="s">
         <v>42</v>
@@ -37183,15 +37330,15 @@
         <v>43</v>
       </c>
       <c r="H149" s="10" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="150" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A150" s="10" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="B150" s="11" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="C150" s="10" t="s">
         <v>42</v>
@@ -37205,15 +37352,15 @@
         <v>43</v>
       </c>
       <c r="H150" s="10" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="151" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A151" s="10" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="B151" s="11" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="C151" s="10" t="s">
         <v>42</v>
@@ -37227,15 +37374,15 @@
         <v>43</v>
       </c>
       <c r="H151" s="10" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
     </row>
     <row r="152" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A152" s="10" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="B152" s="11" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="C152" s="10" t="s">
         <v>42</v>
@@ -37249,15 +37396,15 @@
         <v>43</v>
       </c>
       <c r="H152" s="10" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="153" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A153" s="10" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="B153" s="10" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="C153" s="10" t="s">
         <v>42</v>
@@ -37269,18 +37416,18 @@
       </c>
       <c r="F153" s="10"/>
       <c r="G153" s="10" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="H153" s="10" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="154" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A154" s="10" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="B154" s="11" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="C154" s="10" t="s">
         <v>42</v>
@@ -37294,15 +37441,15 @@
         <v>43</v>
       </c>
       <c r="H154" s="10" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
     </row>
     <row r="155" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A155" s="10" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="B155" s="11" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="C155" s="10" t="s">
         <v>42</v>
@@ -37314,18 +37461,18 @@
       </c>
       <c r="F155" s="10"/>
       <c r="G155" s="10" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="H155" s="10" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
     </row>
     <row r="156" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A156" s="10" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="B156" s="11" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="C156" s="10" t="s">
         <v>42</v>
@@ -37340,15 +37487,15 @@
         <v>43</v>
       </c>
       <c r="H156" s="11" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
     </row>
     <row r="157" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A157" s="10" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="B157" s="11" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="C157" s="10" t="s">
         <v>42</v>
@@ -37363,15 +37510,15 @@
         <v>43</v>
       </c>
       <c r="H157" s="11" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
     </row>
     <row r="158" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A158" s="10" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="B158" s="11" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="C158" s="10" t="s">
         <v>42</v>
@@ -37386,15 +37533,15 @@
         <v>43</v>
       </c>
       <c r="H158" s="11" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
     </row>
     <row r="159" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A159" s="10" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="B159" s="11" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="C159" s="10" t="s">
         <v>42</v>
@@ -37406,18 +37553,18 @@
       </c>
       <c r="F159" s="10"/>
       <c r="G159" s="10" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="H159" s="10" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
     </row>
     <row r="160" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A160" s="10" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="B160" s="11" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="C160" s="10" t="s">
         <v>42</v>
@@ -37429,18 +37576,18 @@
       </c>
       <c r="F160" s="10"/>
       <c r="G160" s="10" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="H160" s="10" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
     </row>
     <row r="161" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A161" s="10" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="B161" s="11" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="C161" s="10" t="s">
         <v>42</v>
@@ -37452,21 +37599,21 @@
       </c>
       <c r="F161" s="10"/>
       <c r="G161" s="10" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="H161" s="10" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
     </row>
     <row r="162" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A162" s="10" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="B162" s="11" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="C162" s="10" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="D162" s="12" t="n">
         <v>2650</v>
@@ -37481,18 +37628,18 @@
         <v>33</v>
       </c>
       <c r="H162" s="10" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
     </row>
     <row r="163" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A163" s="10" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="B163" s="11" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="C163" s="10" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="D163" s="10"/>
       <c r="E163" s="12" t="n">
@@ -37503,18 +37650,18 @@
         <v>33</v>
       </c>
       <c r="H163" s="10" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
     </row>
     <row r="164" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A164" s="10" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="B164" s="11" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="C164" s="10" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="D164" s="10"/>
       <c r="E164" s="12" t="n">
@@ -37525,15 +37672,15 @@
         <v>33</v>
       </c>
       <c r="H164" s="10" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
     </row>
     <row r="165" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A165" s="0" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="B165" s="4" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="C165" s="0" t="s">
         <v>42</v>
@@ -37546,18 +37693,18 @@
         <v>43</v>
       </c>
       <c r="H165" s="8" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="I165" s="4" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
     </row>
     <row r="166" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A166" s="0" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="B166" s="4" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="C166" s="0" t="s">
         <v>42</v>
@@ -37570,10 +37717,10 @@
         <v>43</v>
       </c>
       <c r="H166" s="8" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="I166" s="4" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
     </row>
   </sheetData>
@@ -37601,7 +37748,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="0" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -37609,24 +37756,24 @@
         <v>22</v>
       </c>
       <c r="B3" s="15" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="C3" s="15" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="D3" s="15" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="E3" s="15" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B4" s="16" t="n">
         <f aca="false">u_bw_26/pp_GB*1000</f>
@@ -37647,7 +37794,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="3" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="B5" s="16" t="n">
         <f aca="false">u_rb_26/pp_VR*1000</f>
@@ -37668,7 +37815,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="3" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="B6" s="16" t="n">
         <f aca="false">u_ru_26/pp_RU*1000</f>
@@ -37689,7 +37836,7 @@
     </row>
     <row r="7" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="3" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="B7" s="16" t="n">
         <f aca="false">u_hp_26/pp_HP*1000</f>
@@ -37710,7 +37857,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="3" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="B8" s="16" t="n">
         <f aca="false">u_amd_26/pp_AMD8*1000</f>
@@ -37731,7 +37878,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="3" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="B9" s="16" t="n">
         <f aca="false">u_tpu_26/pp_TPU7*1000</f>
@@ -37752,7 +37899,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="3" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="B10" s="16" t="n">
         <f aca="false">u_trn_26/pp_TRN*1000</f>
@@ -37773,7 +37920,7 @@
     </row>
     <row r="11" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="2" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="B11" s="16" t="n">
         <f aca="false">u_oth_26/pp_ASIC*1000</f>
@@ -37794,7 +37941,7 @@
     </row>
     <row r="12" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="2" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="B12" s="16" t="n">
         <f aca="false">cow_oth26</f>
@@ -37815,7 +37962,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="B13" s="16" t="n">
         <f aca="false">SUM(B4:B12)</f>
@@ -37836,7 +37983,7 @@
     </row>
     <row r="14" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="2" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="B14" s="16" t="n">
         <f aca="false">B4+B5+B6+B7</f>
@@ -37857,7 +38004,7 @@
     </row>
     <row r="15" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="2" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="B15" s="16" t="n">
         <f aca="false">(cap_end25+cap_end26)/2*12</f>
@@ -37878,7 +38025,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="2" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="B16" s="16" t="n">
         <f aca="false">B15*(1+osat)</f>
@@ -37899,7 +38046,7 @@
     </row>
     <row r="17" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="2" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="B17" s="17" t="n">
         <f aca="false">B13/B16</f>
@@ -37918,24 +38065,24 @@
         <v>0.787180222794447</v>
       </c>
       <c r="F17" s="8" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="2" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="C18" s="17" t="n">
         <f aca="false">hbm_gap27</f>
         <v>0.21</v>
       </c>
       <c r="F18" s="8" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="2" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="B19" s="16" t="n">
         <f aca="false">ms_dem26</f>
@@ -37948,7 +38095,7 @@
     </row>
     <row r="20" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="2" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="B20" s="17" t="n">
         <f aca="false">B13/B19-1</f>
@@ -37961,7 +38108,7 @@
     </row>
     <row r="21" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="3" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="B21" s="17" t="n">
         <f aca="false">B14/660-1</f>
@@ -37998,7 +38145,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="0" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -38006,66 +38153,66 @@
         <v>22</v>
       </c>
       <c r="B3" s="15" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="C3" s="15" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="D3" s="15" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="E3" s="15" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="F3" s="15" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="G3" s="15" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="H3" s="15" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="I3" s="15" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="J3" s="15" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="K3" s="15" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="L3" s="15" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="M3" s="15" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="N3" s="15" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="O3" s="15" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="P3" s="15" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="Q3" s="15" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="R3" s="15" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="S3" s="15" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="T3" s="15" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="0" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="B4" s="18" t="n">
         <f aca="false">(u_bw_26*ct_GB+u_rb_26*ct_VR+u_ru_26*ct_RU+u_hp_26*ct_HP+u_amd_26*ct_AMD8+u_tpu_26*ct_TPU7+u_trn_26*ct_TRN+u_oth_26*ct_ASIC)*1</f>
@@ -38110,7 +38257,7 @@
     </row>
     <row r="5" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="B5" s="18" t="n">
         <f aca="false">B4*(1+ai_oth)</f>
@@ -38155,7 +38302,7 @@
     </row>
     <row r="6" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="4" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="B6" s="18" t="n">
         <f aca="false">B7-B5</f>
@@ -38200,7 +38347,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="4" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="B7" s="18" t="n">
         <f aca="false">rev26</f>
@@ -38281,7 +38428,7 @@
     </row>
     <row r="8" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="0" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="B8" s="14" t="n">
         <f aca="false">B5/B7</f>
@@ -38326,7 +38473,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="4" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="B9" s="14" t="n">
         <f aca="false">gm26</f>
@@ -38371,7 +38518,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="4" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="B10" s="18" t="n">
         <f aca="false">B7*B9</f>
@@ -38416,7 +38563,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="4" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="B11" s="18" t="n">
         <f aca="false">B7*(B9-opex_26)</f>
@@ -38461,7 +38608,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="4" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="B12" s="18" t="n">
         <f aca="false">B11*ni_op_26</f>
@@ -38542,7 +38689,7 @@
     </row>
     <row r="13" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="0" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="B13" s="18" t="n">
         <f aca="false">B12*fx_26/shares</f>
@@ -38623,7 +38770,7 @@
     </row>
     <row r="14" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="4" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="B14" s="20" t="n">
         <f aca="false">px/B13</f>
@@ -38704,7 +38851,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="4" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="B15" s="18" t="n">
         <f aca="false">capex26</f>
@@ -38749,7 +38896,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="4" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="B16" s="18" t="n">
         <f aca="false">B12-B15</f>
@@ -38794,17 +38941,17 @@
     </row>
     <row r="18" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="4" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="4" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="4" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="B20" s="14" t="n">
         <f aca="false">B7/rev25-1</f>
@@ -38885,7 +39032,7 @@
     </row>
     <row r="21" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="4" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="B21" s="14" t="n">
         <f aca="false">B12/B7</f>
@@ -38966,7 +39113,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="4" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="B22" s="18" t="n">
         <f aca="false">B12+B7*da_rev-B15</f>
@@ -39047,7 +39194,7 @@
     </row>
     <row r="23" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="4" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
     </row>
   </sheetData>
@@ -39080,45 +39227,45 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="0" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="5" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="C3" s="15" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="E3" s="15" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="G3" s="5" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="0" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="B4" s="0" t="n">
         <f aca="false">pe_1</f>
         <v>15</v>
       </c>
       <c r="C4" s="0" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="D4" s="0" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="E4" s="18" t="n">
         <f aca="false">PL!C13</f>
@@ -39135,17 +39282,17 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="B5" s="0" t="n">
         <f aca="false">pe_2</f>
         <v>20.5</v>
       </c>
       <c r="C5" s="0" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="D5" s="0" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="E5" s="18" t="n">
         <f aca="false">PL!C13</f>
@@ -39162,17 +39309,17 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="B6" s="0" t="n">
         <f aca="false">pe_3</f>
         <v>32.7</v>
       </c>
       <c r="C6" s="0" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="D6" s="0" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="E6" s="18" t="n">
         <f aca="false">PL!C13</f>
@@ -39189,17 +39336,17 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="0" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="B7" s="0" t="n">
         <f aca="false">pe_1</f>
         <v>15</v>
       </c>
       <c r="C7" s="0" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="D7" s="0" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="E7" s="18" t="n">
         <f aca="false">PL!D13</f>
@@ -39216,17 +39363,17 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="0" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="B8" s="0" t="n">
         <f aca="false">pe_2</f>
         <v>20.5</v>
       </c>
       <c r="C8" s="0" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="D8" s="0" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="E8" s="18" t="n">
         <f aca="false">PL!D13</f>
@@ -39243,17 +39390,17 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="0" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="B9" s="0" t="n">
         <f aca="false">pe_3</f>
         <v>32.7</v>
       </c>
       <c r="C9" s="0" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="D9" s="0" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="E9" s="18" t="n">
         <f aca="false">PL!D13</f>
@@ -39270,17 +39417,17 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="0" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="B10" s="0" t="n">
         <f aca="false">pe_1</f>
         <v>15</v>
       </c>
       <c r="C10" s="0" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="D10" s="0" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="E10" s="18" t="n">
         <f aca="false">PL!F13</f>
@@ -39297,17 +39444,17 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="0" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="B11" s="0" t="n">
         <f aca="false">pe_2</f>
         <v>20.5</v>
       </c>
       <c r="C11" s="0" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="D11" s="0" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="E11" s="18" t="n">
         <f aca="false">PL!F13</f>
@@ -39324,17 +39471,17 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="0" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="B12" s="0" t="n">
         <f aca="false">pe_3</f>
         <v>32.7</v>
       </c>
       <c r="C12" s="0" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="D12" s="0" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="E12" s="18" t="n">
         <f aca="false">PL!F13</f>
@@ -39351,17 +39498,17 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="0" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="B13" s="0" t="n">
         <f aca="false">pe_1</f>
         <v>15</v>
       </c>
       <c r="C13" s="0" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="D13" s="0" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="E13" s="18" t="n">
         <f aca="false">PL!G13</f>
@@ -39378,17 +39525,17 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="0" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="B14" s="0" t="n">
         <f aca="false">pe_2</f>
         <v>20.5</v>
       </c>
       <c r="C14" s="0" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="D14" s="0" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="E14" s="18" t="n">
         <f aca="false">PL!G13</f>
@@ -39405,17 +39552,17 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="0" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="B15" s="0" t="n">
         <f aca="false">pe_3</f>
         <v>32.7</v>
       </c>
       <c r="C15" s="0" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="D15" s="0" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="E15" s="18" t="n">
         <f aca="false">PL!G13</f>
@@ -39432,17 +39579,17 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="0" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="B16" s="0" t="n">
         <f aca="false">pe_1</f>
         <v>15</v>
       </c>
       <c r="C16" s="0" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="D16" s="0" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="E16" s="18" t="n">
         <f aca="false">PL!I13</f>
@@ -39459,17 +39606,17 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="0" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="B17" s="0" t="n">
         <f aca="false">pe_2</f>
         <v>20.5</v>
       </c>
       <c r="C17" s="0" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="D17" s="0" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="E17" s="18" t="n">
         <f aca="false">PL!I13</f>
@@ -39486,17 +39633,17 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="0" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="B18" s="0" t="n">
         <f aca="false">pe_3</f>
         <v>32.7</v>
       </c>
       <c r="C18" s="0" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="D18" s="0" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="E18" s="18" t="n">
         <f aca="false">PL!I13</f>
@@ -39513,17 +39660,17 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="0" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="B19" s="0" t="n">
         <f aca="false">pe_1</f>
         <v>15</v>
       </c>
       <c r="C19" s="0" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="D19" s="0" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="E19" s="18" t="n">
         <f aca="false">PL!J13</f>
@@ -39540,17 +39687,17 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="0" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="B20" s="0" t="n">
         <f aca="false">pe_2</f>
         <v>20.5</v>
       </c>
       <c r="C20" s="0" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="D20" s="0" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="E20" s="18" t="n">
         <f aca="false">PL!J13</f>
@@ -39567,17 +39714,17 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="0" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="B21" s="0" t="n">
         <f aca="false">pe_3</f>
         <v>32.7</v>
       </c>
       <c r="C21" s="0" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="D21" s="0" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="E21" s="18" t="n">
         <f aca="false">PL!J13</f>
@@ -39594,41 +39741,41 @@
     </row>
     <row r="23" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="4" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="6" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="4" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="6" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="5" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="B30" s="15" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="C30" s="15" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="D30" s="5" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="0" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="B31" s="23" t="n">
         <v>14.5</v>
@@ -39637,12 +39784,12 @@
         <v>11.6</v>
       </c>
       <c r="D31" s="8" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="0" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="B32" s="23" t="n">
         <v>17.71</v>
@@ -39653,7 +39800,7 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="0" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="B33" s="23" t="n">
         <v>16.13</v>
@@ -39664,7 +39811,7 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="0" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="B34" s="23" t="n">
         <v>25.62</v>
@@ -39675,7 +39822,7 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="0" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="B35" s="23" t="n">
         <v>31.11</v>
@@ -39686,7 +39833,7 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="0" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="B36" s="23" t="n">
         <v>29.18</v>
@@ -39697,7 +39844,7 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="0" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="B37" s="23" t="n">
         <v>11.94</v>
@@ -39708,7 +39855,7 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="0" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="B38" s="23" t="n">
         <v>19.46</v>
@@ -39719,7 +39866,7 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="0" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="B39" s="23" t="n">
         <v>28.72</v>
@@ -39730,7 +39877,7 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="0" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="B40" s="23" t="n">
         <v>29.03</v>
@@ -39741,7 +39888,7 @@
     </row>
     <row r="41" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="0" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="B41" s="24" t="n">
         <f aca="false">PERCENTILE(B31:B40,0.25)</f>
@@ -39754,7 +39901,7 @@
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="4" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="B42" s="24" t="n">
         <f aca="false">MEDIAN(B31:B40)</f>
@@ -39767,7 +39914,7 @@
     </row>
     <row r="43" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="0" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="B43" s="24" t="n">
         <f aca="false">PERCENTILE(B31:B40,0.75)</f>
@@ -39780,7 +39927,7 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="4" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="B44" s="24" t="n">
         <f aca="false">MIN(B31:B40)</f>
@@ -39793,7 +39940,7 @@
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="4" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="B45" s="24" t="n">
         <f aca="false">MAX(B31:B40)</f>
@@ -39806,7 +39953,7 @@
     </row>
     <row r="46" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="1" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="B46" s="24" t="n">
         <f aca="false">ROUND(AVERAGE(B41,C41),2)</f>
@@ -39815,7 +39962,7 @@
     </row>
     <row r="47" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="1" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="B47" s="24" t="n">
         <f aca="false">ROUND(AVERAGE(B42,C42),2)</f>
@@ -39824,7 +39971,7 @@
     </row>
     <row r="48" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="1" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="B48" s="24" t="n">
         <f aca="false">ROUND(AVERAGE(B43,C43),2)</f>
@@ -39833,7 +39980,7 @@
     </row>
     <row r="49" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="1" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="B49" s="24" t="n">
         <f aca="false">ROUND(MIN(B44,C44),2)</f>
@@ -39842,7 +39989,7 @@
     </row>
     <row r="50" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="1" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="B50" s="24" t="n">
         <f aca="false">ROUND(MAX(B45,C45),2)</f>
@@ -39851,48 +39998,48 @@
     </row>
     <row r="52" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="6" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="5" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="C53" s="5" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="D53" s="5" t="s">
         <v>25</v>
       </c>
       <c r="E53" s="5" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="F53" s="5" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="G53" s="5" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="H53" s="5" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="4" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="B54" s="4" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="C54" s="24" t="n">
         <f aca="false">B47</f>
         <v>21.97</v>
       </c>
       <c r="D54" s="8" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="E54" s="18" t="n">
         <f aca="false">PL!C13</f>
@@ -39913,17 +40060,17 @@
     </row>
     <row r="55" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="4" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="B55" s="0" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="C55" s="24" t="n">
         <f aca="false">B46</f>
         <v>15.44</v>
       </c>
       <c r="D55" s="8" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="E55" s="18" t="n">
         <f aca="false">PL!C13</f>
@@ -39944,17 +40091,17 @@
     </row>
     <row r="56" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="4" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="B56" s="0" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="C56" s="24" t="n">
         <f aca="false">B48</f>
         <v>28.49</v>
       </c>
       <c r="D56" s="8" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="E56" s="18" t="n">
         <f aca="false">PL!C13</f>
@@ -39975,17 +40122,17 @@
     </row>
     <row r="57" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="4" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="B57" s="4" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="C57" s="24" t="n">
         <f aca="false">B48</f>
         <v>28.49</v>
       </c>
       <c r="D57" s="8" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="E57" s="18" t="n">
         <f aca="false">PL!J13</f>
@@ -40006,12 +40153,12 @@
     </row>
     <row r="59" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="6" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="6" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -40019,29 +40166,29 @@
         <v>22</v>
       </c>
       <c r="B61" s="15" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="C61" s="15" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="D61" s="15" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="E61" s="5" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="4" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="E62" s="0" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="0" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="B63" s="24" t="n">
         <f aca="false">PL!C13</f>
@@ -40058,7 +40205,7 @@
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="0" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="B64" s="24" t="n">
         <f aca="false">PL!D13</f>
@@ -40075,7 +40222,7 @@
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="0" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="B65" s="24" t="n">
         <f aca="false">PL!E13</f>
@@ -40092,7 +40239,7 @@
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="0" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="B66" s="24" t="n">
         <f aca="false">PL!L13</f>
@@ -40109,7 +40256,7 @@
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="0" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="B67" s="24" t="n">
         <f aca="false">PL!M13</f>
@@ -40126,7 +40273,7 @@
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="0" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="B68" s="24" t="n">
         <f aca="false">PL!N13</f>
@@ -40143,27 +40290,27 @@
     </row>
     <row r="69" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="4" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="E69" s="4" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="4" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="B70" s="14" t="n">
         <f aca="false">MIN(tp_g/tp_roe,0.8)</f>
         <v>0.130875777074926</v>
       </c>
       <c r="E70" s="8" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="0" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="B71" s="24" t="n">
         <f aca="false">B63*(1-$B$70)</f>
@@ -40180,7 +40327,7 @@
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="0" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="B72" s="24" t="n">
         <f aca="false">B64*(1-$B$70)</f>
@@ -40197,7 +40344,7 @@
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="0" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="B73" s="24" t="n">
         <f aca="false">B65*(1-$B$70)</f>
@@ -40214,7 +40361,7 @@
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="0" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="B74" s="24" t="n">
         <f aca="false">B66*(1-$B$70)</f>
@@ -40231,7 +40378,7 @@
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="0" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="B75" s="24" t="n">
         <f aca="false">B67*(1-$B$70)</f>
@@ -40248,7 +40395,7 @@
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="0" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="B76" s="24" t="n">
         <f aca="false">B68*(1-$B$70)</f>
@@ -40265,7 +40412,7 @@
     </row>
     <row r="77" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="0" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="B77" s="16" t="n">
         <f aca="false">SUMPRODUCT(B71:B76,1/(1+tp_r)^{1;2;3;4;5;6})+B76*(1+tp_g)/(tp_r-tp_g)/(1+tp_r)^6</f>
@@ -40280,12 +40427,12 @@
         <v>1359.89907002946</v>
       </c>
       <c r="E77" s="8" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="0" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="B78" s="16" t="n">
         <f aca="false">B77*(1+tp_r)</f>
@@ -40302,36 +40449,36 @@
     </row>
     <row r="79" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="0" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="B79" s="26" t="n">
         <f aca="false">tp_wA*B78+tp_wB*C78+tp_wC*D78</f>
         <v>2150.17798362528</v>
       </c>
       <c r="E79" s="8" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="6" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="5" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="B82" s="5" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="C82" s="5" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="D82" s="5" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="E82" s="5" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="F82" s="5" t="s">
         <v>27</v>
@@ -40339,19 +40486,19 @@
     </row>
     <row r="83" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="4" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="B83" s="0" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="C83" s="27" t="n">
         <v>20.46</v>
       </c>
       <c r="D83" s="8" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="E83" s="8" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="F83" s="8" t="s">
         <v>33</v>
@@ -40359,19 +40506,19 @@
     </row>
     <row r="84" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="4" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="B84" s="0" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="C84" s="27" t="n">
         <v>20.04</v>
       </c>
       <c r="D84" s="8" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="E84" s="8" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="F84" s="8" t="s">
         <v>33</v>
@@ -40379,19 +40526,19 @@
     </row>
     <row r="85" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="4" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="B85" s="0" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="C85" s="27" t="n">
         <v>50.64</v>
       </c>
       <c r="D85" s="8" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="E85" s="8" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="F85" s="8" t="s">
         <v>33</v>
@@ -40399,19 +40546,19 @@
     </row>
     <row r="86" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="4" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="B86" s="0" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="C86" s="27" t="n">
         <v>37.14</v>
       </c>
       <c r="D86" s="8" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="E86" s="8" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="F86" s="8" t="s">
         <v>33</v>
@@ -40419,19 +40566,19 @@
     </row>
     <row r="87" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="4" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="B87" s="0" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="C87" s="27" t="n">
         <v>3.35</v>
       </c>
       <c r="D87" s="8" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="E87" s="8" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="F87" s="8" t="s">
         <v>33</v>
@@ -40439,43 +40586,43 @@
     </row>
     <row r="88" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="4" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="B88" s="18" t="n">
         <f aca="false">MEDIAN(C83:C87)</f>
         <v>20.46</v>
       </c>
       <c r="E88" s="4" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="0" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="B89" s="24" t="n">
         <f aca="false">tp_wA*(2/12*B63+10/12*B64)+tp_wB*(2/12*C63+10/12*C64)+tp_wC*(2/12*D63+10/12*D64)</f>
         <v>134.011173721684</v>
       </c>
       <c r="E89" s="4" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="0" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="B90" s="26" t="n">
         <f aca="false">B88*B89</f>
         <v>2741.86861434566</v>
       </c>
       <c r="E90" s="4" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="6" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -40483,29 +40630,29 @@
         <v>22</v>
       </c>
       <c r="B93" s="5" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="C93" s="5"/>
       <c r="D93" s="5"/>
       <c r="E93" s="5" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="4" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="B94" s="26" t="n">
         <f aca="false">tp_w_dcf*B79+(1-tp_w_dcf)*B90</f>
         <v>2446.02329898547</v>
       </c>
       <c r="E94" s="8" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="0" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="B95" s="16" t="n">
         <f aca="false">B90</f>
@@ -40514,31 +40661,31 @@
     </row>
     <row r="96" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="4" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="B96" s="16" t="n">
         <f aca="false">cons_tp</f>
         <v>3390.43</v>
       </c>
       <c r="E96" s="8" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="4" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="B97" s="14" t="n">
         <f aca="false">B94/px-1</f>
         <v>0.0255862888827967</v>
       </c>
       <c r="E97" s="4" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="4" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="B98" s="14" t="n">
         <f aca="false">B95/px-1</f>
@@ -40547,19 +40694,19 @@
     </row>
     <row r="99" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="4" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="B99" s="14" t="n">
         <f aca="false">B89/(2/12*cons_feps27+10/12*cons_feps28)-1</f>
         <v>-0.261714220613254</v>
       </c>
       <c r="E99" s="4" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A100" s="4" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="B100" s="14" t="n">
         <f aca="false">(cons_tp/(2/12*cons_feps27+10/12*cons_feps28))/B88-1</f>
@@ -40572,19 +40719,19 @@
     </row>
     <row r="101" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A101" s="4" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="B101" s="28" t="str">
         <f aca="false">TEXT(D78,"#,##0")&amp;"～"&amp;TEXT(B78,"#,##0")</f>
         <v>1,496～2,769</v>
       </c>
       <c r="E101" s="8" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
     </row>
     <row r="102" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A102" s="4" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="B102" s="17" t="n">
         <f aca="false">IF(px/B64&gt;=MAX($C$31:$C$40),1,IF(px/B64&lt;=MIN($C$31:$C$40),0,PERCENTRANK($C$31:$C$40,px/B64)))</f>
@@ -40599,20 +40746,20 @@
         <v>0.527</v>
       </c>
       <c r="E102" s="4" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
     </row>
     <row r="103" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A103" s="4" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="B103" s="0" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
     </row>
     <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A105" s="1" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
     </row>
     <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -40620,29 +40767,29 @@
         <v>22</v>
       </c>
       <c r="B106" s="5" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="C106" s="5"/>
       <c r="D106" s="5"/>
       <c r="E106" s="5" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
     </row>
     <row r="107" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A107" s="4" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="B107" s="16" t="n">
         <f aca="false">tp_wA*B109+tp_wB*B110+tp_wC*B111</f>
         <v>3022.97680876707</v>
       </c>
       <c r="E107" s="4" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
     </row>
     <row r="108" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A108" s="4" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="B108" s="14" t="n">
         <f aca="false">B107/px-1</f>
@@ -40651,43 +40798,43 @@
     </row>
     <row r="109" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A109" s="4" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="B109" s="16" t="n">
         <f aca="false">$C$54*PL!C13</f>
         <v>3022.97680876707</v>
       </c>
       <c r="E109" s="4" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
     </row>
     <row r="110" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A110" s="4" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="B110" s="16" t="n">
         <f aca="false">$C$54*PL!F13</f>
         <v>3022.97680876707</v>
       </c>
       <c r="E110" s="4" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
     </row>
     <row r="111" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A111" s="4" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="B111" s="16" t="n">
         <f aca="false">$C$54*PL!I13</f>
         <v>3022.97680876707</v>
       </c>
       <c r="E111" s="4" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
     </row>
     <row r="112" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A112" s="4" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="B112" s="17" t="n">
         <f aca="false">tp_wA</f>
@@ -40708,34 +40855,34 @@
     </row>
     <row r="113" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A113" s="4" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="B113" s="4" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
     </row>
     <row r="115" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A115" s="4" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="B115" s="28" t="str">
         <f aca="false">IF(B97&gt;0.5,"大於 50%",IF(B97&gt;0.25,"25%–50%",IF(B97&gt;=0,"0%–25%",IF(B97&gt;=-0.25,"0%～−25%",IF(B97&gt;=-0.5,"−25%～−50%","小於 −50%")))))</f>
         <v>0%–25%</v>
       </c>
       <c r="E115" s="4" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
     </row>
     <row r="116" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A116" s="4" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="B116" s="28" t="str">
         <f aca="false">IF(B97&gt;0.5,"強力買進",IF(B97&gt;0.25,"買進",IF(B97&gt;=-0.25,"中立",IF(B97&gt;=-0.5,"放空","強力放空"))))</f>
         <v>中立</v>
       </c>
       <c r="E116" s="4" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
     </row>
   </sheetData>
@@ -40763,7 +40910,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="0" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -40771,21 +40918,21 @@
         <v>22</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="0" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="B4" s="25" t="n">
         <f aca="false">PL!B5</f>
@@ -40800,12 +40947,12 @@
         <v>-0.00788231517711135</v>
       </c>
       <c r="E4" s="8" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="B5" s="25" t="n">
         <f aca="false">PL!B4</f>
@@ -40820,12 +40967,12 @@
         <v>-0.173235262647593</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="B6" s="25" t="n">
         <f aca="false">PL!B13</f>
@@ -40840,12 +40987,12 @@
         <v>0.0417778779533982</v>
       </c>
       <c r="E6" s="8" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="0" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="B7" s="25" t="n">
         <f aca="false">PL!B7</f>
@@ -40860,12 +41007,12 @@
         <v>-0.00101645384664262</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="0" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="B8" s="25" t="n">
         <f aca="false">PL!B13</f>
@@ -40880,12 +41027,12 @@
         <v>-5.0502654148521E-005</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="0" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="B9" s="25" t="n">
         <f aca="false">PL!C7</f>
@@ -40900,12 +41047,12 @@
         <v>-0.0147032314410479</v>
       </c>
       <c r="E9" s="8" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="0" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="B10" s="25" t="n">
         <f aca="false">PL!C13</f>
@@ -40920,12 +41067,12 @@
         <v>-0.0310164280462261</v>
       </c>
       <c r="E10" s="8" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="0" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="B11" s="25" t="n">
         <f aca="false">CoWoS!B13</f>
@@ -40940,12 +41087,12 @@
         <v>-0.205267126392436</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="0" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="B12" s="25" t="n">
         <f aca="false">CoWoS!C13</f>
@@ -40960,12 +41107,12 @@
         <v>-0.16443659966976</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="0" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="B13" s="25" t="n">
         <f aca="false">PL!C13</f>
@@ -40980,12 +41127,12 @@
         <v>-0.0709272976540452</v>
       </c>
       <c r="E13" s="8" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="0" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="B14" s="25" t="n">
         <f aca="false">PL!D13</f>
@@ -41000,7 +41147,7 @@
         <v>-0.162378931418392</v>
       </c>
       <c r="E14" s="8" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
     </row>
   </sheetData>
@@ -41028,21 +41175,21 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="0" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="5" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="B3" s="15" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="D3" s="15" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -41064,7 +41211,7 @@
     </row>
     <row r="5" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="B5" s="18" t="n">
         <f aca="false">(PL!C7-0.3*u_rb_27*ct_VR*(1+px27)*(1+ai_oth))*(gm27_A-opex)*ni_op*fx/shares</f>
@@ -41081,7 +41228,7 @@
     </row>
     <row r="6" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="B6" s="18" t="n">
         <f aca="false">(PL!C7-PL!C5*px27/(1+px27))*(gm27_A-opex)*ni_op*fx/shares</f>
@@ -41098,7 +41245,7 @@
     </row>
     <row r="7" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="4" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="B7" s="18" t="n">
         <f aca="false">(PL!C7)*(0.6-opex)*ni_op*fx/shares</f>
@@ -41115,7 +41262,7 @@
     </row>
     <row r="8" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="4" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="B8" s="18" t="n">
         <f aca="false">(PL!C7)*(0.67-opex)*ni_op*fx/shares</f>
@@ -41132,7 +41279,7 @@
     </row>
     <row r="9" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="4" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="B9" s="18" t="n">
         <f aca="false">(PL!C7-PL!B6*na27_A)*(gm27_A-opex)*ni_op*fx/shares</f>
@@ -41149,7 +41296,7 @@
     </row>
     <row r="10" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="0" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="B10" s="18" t="n">
         <f aca="false">(PL!C7)*(gm27_A-opex)*ni_op*fx/shares</f>
@@ -41166,32 +41313,32 @@
     </row>
     <row r="13" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="5" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="C14" s="15" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="E14" s="15" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="F14" s="5" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="4" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="B15" s="9" t="n">
         <f aca="false">ni_op</f>
@@ -41216,7 +41363,7 @@
     </row>
     <row r="16" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="4" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="B16" s="9" t="n">
         <f aca="false">ni_op_lo</f>
@@ -41241,7 +41388,7 @@
     </row>
     <row r="17" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="4" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="B17" s="9" t="n">
         <f aca="false">ni_op_hi</f>
@@ -41266,27 +41413,27 @@
     </row>
     <row r="21" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="5" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="C22" s="15" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="D22" s="15" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="F22" s="5" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -41294,7 +41441,7 @@
         <v>25</v>
       </c>
       <c r="B23" s="0" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="C23" s="16" t="n">
         <f aca="false">(tp_wA*(Val!B63*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^1+Val!B64*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^2+Val!B65*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^3+Val!B66*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^4+Val!B67*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^5+Val!B68*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^6+Val!B68*(1-MIN(tp_g/tp_roe,0.8))*(1+tp_g)/(tp_r-tp_g)/(1+tp_r)^6)+tp_wB*(Val!C63*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^1+Val!C64*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^2+Val!C65*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^3+Val!C66*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^4+Val!C67*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^5+Val!C68*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^6+Val!C68*(1-MIN(tp_g/tp_roe,0.8))*(1+tp_g)/(tp_r-tp_g)/(1+tp_r)^6)+tp_wC*(Val!D63*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^1+Val!D64*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^2+Val!D65*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^3+Val!D66*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^4+Val!D67*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^5+Val!D68*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^6+Val!D68*(1-MIN(tp_g/tp_roe,0.8))*(1+tp_g)/(tp_r-tp_g)/(1+tp_r)^6))*(1+tp_r)</f>
@@ -41315,10 +41462,10 @@
     </row>
     <row r="24" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="4" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="B24" s="0" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="C24" s="16" t="n">
         <f aca="false">(tp_wA*(Val!B63*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r+0.01))^1+Val!B64*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r+0.01))^2+Val!B65*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r+0.01))^3+Val!B66*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r+0.01))^4+Val!B67*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r+0.01))^5+Val!B68*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r+0.01))^6+Val!B68*(1-MIN(tp_g/tp_roe,0.8))*(1+tp_g)/((tp_r+0.01)-tp_g)/(1+(tp_r+0.01))^6)+tp_wB*(Val!C63*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r+0.01))^1+Val!C64*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r+0.01))^2+Val!C65*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r+0.01))^3+Val!C66*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r+0.01))^4+Val!C67*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r+0.01))^5+Val!C68*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r+0.01))^6+Val!C68*(1-MIN(tp_g/tp_roe,0.8))*(1+tp_g)/((tp_r+0.01)-tp_g)/(1+(tp_r+0.01))^6)+tp_wC*(Val!D63*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r+0.01))^1+Val!D64*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r+0.01))^2+Val!D65*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r+0.01))^3+Val!D66*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r+0.01))^4+Val!D67*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r+0.01))^5+Val!D68*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r+0.01))^6+Val!D68*(1-MIN(tp_g/tp_roe,0.8))*(1+tp_g)/((tp_r+0.01)-tp_g)/(1+(tp_r+0.01))^6))*(1+(tp_r+0.01))</f>
@@ -41339,10 +41486,10 @@
     </row>
     <row r="25" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="4" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="B25" s="0" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="C25" s="16" t="n">
         <f aca="false">(tp_wA*(Val!B63*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r-0.01))^1+Val!B64*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r-0.01))^2+Val!B65*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r-0.01))^3+Val!B66*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r-0.01))^4+Val!B67*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r-0.01))^5+Val!B68*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r-0.01))^6+Val!B68*(1-MIN(tp_g/tp_roe,0.8))*(1+tp_g)/((tp_r-0.01)-tp_g)/(1+(tp_r-0.01))^6)+tp_wB*(Val!C63*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r-0.01))^1+Val!C64*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r-0.01))^2+Val!C65*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r-0.01))^3+Val!C66*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r-0.01))^4+Val!C67*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r-0.01))^5+Val!C68*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r-0.01))^6+Val!C68*(1-MIN(tp_g/tp_roe,0.8))*(1+tp_g)/((tp_r-0.01)-tp_g)/(1+(tp_r-0.01))^6)+tp_wC*(Val!D63*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r-0.01))^1+Val!D64*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r-0.01))^2+Val!D65*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r-0.01))^3+Val!D66*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r-0.01))^4+Val!D67*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r-0.01))^5+Val!D68*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r-0.01))^6+Val!D68*(1-MIN(tp_g/tp_roe,0.8))*(1+tp_g)/((tp_r-0.01)-tp_g)/(1+(tp_r-0.01))^6))*(1+(tp_r-0.01))</f>
@@ -41363,10 +41510,10 @@
     </row>
     <row r="26" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="4" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="B26" s="0" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="C26" s="16" t="n">
         <f aca="false">(tp_wA*(Val!B63*(1-MIN((tp_g+0.01)/tp_roe,0.8))/(1+tp_r)^1+Val!B64*(1-MIN((tp_g+0.01)/tp_roe,0.8))/(1+tp_r)^2+Val!B65*(1-MIN((tp_g+0.01)/tp_roe,0.8))/(1+tp_r)^3+Val!B66*(1-MIN((tp_g+0.01)/tp_roe,0.8))/(1+tp_r)^4+Val!B67*(1-MIN((tp_g+0.01)/tp_roe,0.8))/(1+tp_r)^5+Val!B68*(1-MIN((tp_g+0.01)/tp_roe,0.8))/(1+tp_r)^6+Val!B68*(1-MIN((tp_g+0.01)/tp_roe,0.8))*(1+(tp_g+0.01))/(tp_r-(tp_g+0.01))/(1+tp_r)^6)+tp_wB*(Val!C63*(1-MIN((tp_g+0.01)/tp_roe,0.8))/(1+tp_r)^1+Val!C64*(1-MIN((tp_g+0.01)/tp_roe,0.8))/(1+tp_r)^2+Val!C65*(1-MIN((tp_g+0.01)/tp_roe,0.8))/(1+tp_r)^3+Val!C66*(1-MIN((tp_g+0.01)/tp_roe,0.8))/(1+tp_r)^4+Val!C67*(1-MIN((tp_g+0.01)/tp_roe,0.8))/(1+tp_r)^5+Val!C68*(1-MIN((tp_g+0.01)/tp_roe,0.8))/(1+tp_r)^6+Val!C68*(1-MIN((tp_g+0.01)/tp_roe,0.8))*(1+(tp_g+0.01))/(tp_r-(tp_g+0.01))/(1+tp_r)^6)+tp_wC*(Val!D63*(1-MIN((tp_g+0.01)/tp_roe,0.8))/(1+tp_r)^1+Val!D64*(1-MIN((tp_g+0.01)/tp_roe,0.8))/(1+tp_r)^2+Val!D65*(1-MIN((tp_g+0.01)/tp_roe,0.8))/(1+tp_r)^3+Val!D66*(1-MIN((tp_g+0.01)/tp_roe,0.8))/(1+tp_r)^4+Val!D67*(1-MIN((tp_g+0.01)/tp_roe,0.8))/(1+tp_r)^5+Val!D68*(1-MIN((tp_g+0.01)/tp_roe,0.8))/(1+tp_r)^6+Val!D68*(1-MIN((tp_g+0.01)/tp_roe,0.8))*(1+(tp_g+0.01))/(tp_r-(tp_g+0.01))/(1+tp_r)^6))*(1+tp_r)</f>
@@ -41387,10 +41534,10 @@
     </row>
     <row r="27" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="4" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="B27" s="0" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="C27" s="16" t="n">
         <f aca="false">(tp_wA*(Val!B63*(1-MIN((tp_g-0.01)/tp_roe,0.8))/(1+tp_r)^1+Val!B64*(1-MIN((tp_g-0.01)/tp_roe,0.8))/(1+tp_r)^2+Val!B65*(1-MIN((tp_g-0.01)/tp_roe,0.8))/(1+tp_r)^3+Val!B66*(1-MIN((tp_g-0.01)/tp_roe,0.8))/(1+tp_r)^4+Val!B67*(1-MIN((tp_g-0.01)/tp_roe,0.8))/(1+tp_r)^5+Val!B68*(1-MIN((tp_g-0.01)/tp_roe,0.8))/(1+tp_r)^6+Val!B68*(1-MIN((tp_g-0.01)/tp_roe,0.8))*(1+(tp_g-0.01))/(tp_r-(tp_g-0.01))/(1+tp_r)^6)+tp_wB*(Val!C63*(1-MIN((tp_g-0.01)/tp_roe,0.8))/(1+tp_r)^1+Val!C64*(1-MIN((tp_g-0.01)/tp_roe,0.8))/(1+tp_r)^2+Val!C65*(1-MIN((tp_g-0.01)/tp_roe,0.8))/(1+tp_r)^3+Val!C66*(1-MIN((tp_g-0.01)/tp_roe,0.8))/(1+tp_r)^4+Val!C67*(1-MIN((tp_g-0.01)/tp_roe,0.8))/(1+tp_r)^5+Val!C68*(1-MIN((tp_g-0.01)/tp_roe,0.8))/(1+tp_r)^6+Val!C68*(1-MIN((tp_g-0.01)/tp_roe,0.8))*(1+(tp_g-0.01))/(tp_r-(tp_g-0.01))/(1+tp_r)^6)+tp_wC*(Val!D63*(1-MIN((tp_g-0.01)/tp_roe,0.8))/(1+tp_r)^1+Val!D64*(1-MIN((tp_g-0.01)/tp_roe,0.8))/(1+tp_r)^2+Val!D65*(1-MIN((tp_g-0.01)/tp_roe,0.8))/(1+tp_r)^3+Val!D66*(1-MIN((tp_g-0.01)/tp_roe,0.8))/(1+tp_r)^4+Val!D67*(1-MIN((tp_g-0.01)/tp_roe,0.8))/(1+tp_r)^5+Val!D68*(1-MIN((tp_g-0.01)/tp_roe,0.8))/(1+tp_r)^6+Val!D68*(1-MIN((tp_g-0.01)/tp_roe,0.8))*(1+(tp_g-0.01))/(tp_r-(tp_g-0.01))/(1+tp_r)^6))*(1+tp_r)</f>
@@ -41411,10 +41558,10 @@
     </row>
     <row r="28" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="0" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="B28" s="0" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="C28" s="16" t="n">
         <f aca="false">(tp_wA*(Val!B63*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^1+Val!B64*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^2+Val!B65*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^3+Val!B66*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^4+Val!B67*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^5+Val!B68*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^6+Val!B68*(1-MIN(tp_g/tp_roe,0.8))*(1+tp_g)/(tp_r-tp_g)/(1+tp_r)^6)+tp_wB*(Val!C63*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^1+Val!C64*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^2+Val!C65*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^3+Val!C66*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^4+Val!C67*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^5+Val!C68*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^6+Val!C68*(1-MIN(tp_g/tp_roe,0.8))*(1+tp_g)/(tp_r-tp_g)/(1+tp_r)^6)+tp_wC*(Val!D63*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^1+Val!D64*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^2+Val!D65*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^3+Val!D66*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^4+Val!D67*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^5+Val!D68*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^6+Val!D68*(1-MIN(tp_g/tp_roe,0.8))*(1+tp_g)/(tp_r-tp_g)/(1+tp_r)^6))*(1+tp_r)</f>
@@ -41435,10 +41582,10 @@
     </row>
     <row r="29" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="0" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="B29" s="0" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="C29" s="16" t="n">
         <f aca="false">(tp_wA*(Val!B63*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^1+Val!B64*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^2+Val!B65*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^3+Val!B66*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^4+Val!B67*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^5+Val!B68*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^6+Val!B68*(1-MIN(tp_g/tp_roe,0.8))*(1+tp_g)/(tp_r-tp_g)/(1+tp_r)^6)+tp_wB*(Val!C63*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^1+Val!C64*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^2+Val!C65*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^3+Val!C66*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^4+Val!C67*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^5+Val!C68*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^6+Val!C68*(1-MIN(tp_g/tp_roe,0.8))*(1+tp_g)/(tp_r-tp_g)/(1+tp_r)^6)+tp_wC*(Val!D63*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^1+Val!D64*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^2+Val!D65*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^3+Val!D66*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^4+Val!D67*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^5+Val!D68*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^6+Val!D68*(1-MIN(tp_g/tp_roe,0.8))*(1+tp_g)/(tp_r-tp_g)/(1+tp_r)^6))*(1+tp_r)</f>
@@ -41459,7 +41606,7 @@
     </row>
     <row r="30" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="4" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="C30" s="29" t="n">
         <f aca="false">C23-Val!B79</f>
@@ -41493,51 +41640,51 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="0" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="5" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="G3" s="5" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="H3" s="5" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="I3" s="5" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="J3" s="5" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="K3" s="5" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="L3" s="5" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="M3" s="5" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="N3" s="5" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="O3" s="5" t="s">
         <v>27</v>
@@ -41548,7 +41695,7 @@
     </row>
     <row r="4" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="0" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="B4" s="30" t="n">
         <v>1121.28</v>
@@ -41592,15 +41739,15 @@
         <v>1</v>
       </c>
       <c r="O4" s="8" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="P4" s="4" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="B5" s="30" t="n">
         <v>921.47</v>
@@ -41645,15 +41792,15 @@
         <v>2</v>
       </c>
       <c r="O5" s="8" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="P5" s="4" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="B6" s="30" t="n">
         <v>1322.05</v>
@@ -41700,15 +41847,15 @@
         <v>2</v>
       </c>
       <c r="O6" s="8" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="P6" s="4" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="0" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="B7" s="30" t="n">
         <v>1936.09</v>
@@ -41755,15 +41902,15 @@
         <v>2</v>
       </c>
       <c r="O7" s="8" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="P7" s="4" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="0" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="B8" s="25" t="n">
         <f aca="false">ntd26_1q*opm26_1q</f>
@@ -41808,15 +41955,15 @@
         <v>1</v>
       </c>
       <c r="O8" s="8" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="P8" s="4" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="0" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="B9" s="25" t="n">
         <f aca="false">ntd26_2q*opm26_2q</f>
@@ -41860,15 +42007,15 @@
         <v>2</v>
       </c>
       <c r="O9" s="8" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="P9" s="4" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="0" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="B10" s="30" t="n">
         <v>876.45</v>
@@ -41911,15 +42058,15 @@
         <v>2</v>
       </c>
       <c r="O10" s="8" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="P10" s="4" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="0" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="B11" s="25" t="n">
         <f aca="false">SUM(B8:B10)</f>
@@ -41964,56 +42111,56 @@
         <v>0.887328973543092</v>
       </c>
       <c r="O11" s="8" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="P11" s="4" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="4" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="B14" s="14" t="n">
         <f aca="false">(E6+E7+E11)/(D6+D7+D11)</f>
         <v>0.165580350953154</v>
       </c>
       <c r="P14" s="4" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="4" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="B15" s="14" t="n">
         <f aca="false">(SUM(C4:C7)+C11-I11)/(SUM(B4:B7)+B11)</f>
         <v>0.0481460113069807</v>
       </c>
       <c r="P15" s="4" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="4" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="B16" s="9" t="n">
         <f aca="false">(1+B15)*(1-B14)</f>
         <v>0.874593626904623</v>
       </c>
       <c r="P16" s="4" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="4" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="B17" s="9" t="n">
         <f aca="false">(F6+F7)/(B6+B7)</f>
@@ -42022,72 +42169,72 @@
     </row>
     <row r="18" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="4" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="B18" s="9" t="n">
         <f aca="false">M11</f>
         <v>0.887328973543092</v>
       </c>
       <c r="P18" s="4" t="s">
-        <v>754</v>
+        <v>755</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="4" t="s">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="B19" s="9" t="n">
         <f aca="false">(F11-I11*(1-B14))/B11</f>
         <v>0.864414533026079</v>
       </c>
       <c r="P19" s="8" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="4" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="B20" s="9" t="n">
         <f aca="false">M5</f>
         <v>0.909166874667651</v>
       </c>
       <c r="P20" s="8" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="4" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="B21" s="14" t="n">
         <f aca="false">(SUM(C4:C7)+C11)/(SUM(B4:B7)+B11)</f>
         <v>0.0564592945007984</v>
       </c>
       <c r="P21" s="4" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="4" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="B22" s="9" t="n">
         <f aca="false">(1+B21)*(1-B14)</f>
         <v>0.881530393749635</v>
       </c>
       <c r="P22" s="4" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="4" t="s">
-        <v>763</v>
+        <v>764</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="4" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
     </row>
   </sheetData>
@@ -42115,332 +42262,332 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="4" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="B2" s="0" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="4" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="B3" s="0" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="B4" s="0" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="4" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="B5" s="0" t="s">
-        <v>772</v>
+        <v>773</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="s">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="B6" s="0" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="0" t="s">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="B7" s="0" t="s">
-        <v>776</v>
+        <v>777</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="4" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="B8" s="0" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="0" t="s">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="B9" s="0" t="s">
-        <v>780</v>
+        <v>781</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="4" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="B10" s="0" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="0" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="B11" s="0" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="0" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="B12" s="0" t="s">
-        <v>786</v>
+        <v>787</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="0" t="s">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="B13" s="0" t="s">
-        <v>788</v>
+        <v>789</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="4" t="s">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="B14" s="0" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="4" t="s">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="B15" s="0" t="s">
-        <v>792</v>
+        <v>793</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="4" t="s">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="B16" s="0" t="s">
-        <v>794</v>
+        <v>795</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="4" t="s">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="B17" s="0" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="4" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="B18" s="0" t="s">
-        <v>798</v>
+        <v>799</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="4" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="B19" s="0" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="4" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="B20" s="0" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="4" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="B21" s="0" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="4" t="s">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="B22" s="0" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="4" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="B23" s="0" t="s">
-        <v>808</v>
+        <v>809</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="4" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="B24" s="0" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="4" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="B25" s="0" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="4" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="B26" s="0" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="4" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="B27" s="0" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="4" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="B28" s="0" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="4" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="B29" s="0" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="4" t="s">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="B30" s="0" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="4" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="B31" s="0" t="s">
-        <v>824</v>
+        <v>825</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="4" t="s">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="B32" s="0" t="s">
-        <v>826</v>
+        <v>827</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="4" t="s">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="B33" s="0" t="s">
-        <v>828</v>
+        <v>829</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="4" t="s">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="B34" s="0" t="s">
-        <v>794</v>
+        <v>795</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="4" t="s">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="B35" s="0" t="s">
-        <v>831</v>
+        <v>832</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="4" t="s">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="B36" s="0" t="s">
-        <v>833</v>
+        <v>834</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="4" t="s">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="B37" s="0" t="s">
-        <v>835</v>
+        <v>836</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="4" t="s">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="B38" s="0" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="4" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="0" t="s">
-        <v>840</v>
+        <v>841</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="0" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="B41" s="0" t="s">
-        <v>842</v>
+        <v>843</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="0" t="s">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>844</v>
+        <v>845</v>
       </c>
     </row>
   </sheetData>

--- a/tsmc/dist/20261025_台積電模型_v0.3.1.xlsx
+++ b/tsmc/dist/20261025_台積電模型_v0.3.1.xlsx
@@ -5371,7 +5371,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">Siliconomics v0.2 SIF_g29_bw</t>
+      <t xml:space="preserve">Siliconomics SIF_g29_bw</t>
     </r>
     <r>
       <rPr>

--- a/tsmc/dist/20261025_台積電模型_v0.3.1.xlsx
+++ b/tsmc/dist/20261025_台積電模型_v0.3.1.xlsx
@@ -33,6 +33,8 @@
     <definedName function="false" hidden="false" name="cap_end27" vbProcedure="false">In!$E$69</definedName>
     <definedName function="false" hidden="false" name="cap_end28" vbProcedure="false">In!$E$70</definedName>
     <definedName function="false" hidden="false" name="cap_end29" vbProcedure="false">In!$E$71</definedName>
+    <definedName function="false" hidden="false" name="cap_end29_hi" vbProcedure="false">In!$F$71</definedName>
+    <definedName function="false" hidden="false" name="cap_end29_lo" vbProcedure="false">In!$D$71</definedName>
     <definedName function="false" hidden="false" name="cons_eps26" vbProcedure="false">In!$E$144</definedName>
     <definedName function="false" hidden="false" name="cons_eps27" vbProcedure="false">In!$E$145</definedName>
     <definedName function="false" hidden="false" name="cons_feps27" vbProcedure="false">In!$E$163</definedName>
@@ -42,7 +44,11 @@
     <definedName function="false" hidden="false" name="cons_tp_hi" vbProcedure="false">In!$F$162</definedName>
     <definedName function="false" hidden="false" name="cons_tp_lo" vbProcedure="false">In!$D$162</definedName>
     <definedName function="false" hidden="false" name="cow_oth26" vbProcedure="false">In!$E$64</definedName>
+    <definedName function="false" hidden="false" name="cow_oth26_hi" vbProcedure="false">In!$F$64</definedName>
+    <definedName function="false" hidden="false" name="cow_oth26_lo" vbProcedure="false">In!$D$64</definedName>
     <definedName function="false" hidden="false" name="cow_oth_g" vbProcedure="false">In!$E$65</definedName>
+    <definedName function="false" hidden="false" name="cow_oth_g_hi" vbProcedure="false">In!$F$65</definedName>
+    <definedName function="false" hidden="false" name="cow_oth_g_lo" vbProcedure="false">In!$D$65</definedName>
     <definedName function="false" hidden="false" name="ct_AMD8" vbProcedure="false">In!$E$53</definedName>
     <definedName function="false" hidden="false" name="ct_AMD8_hi" vbProcedure="false">In!$F$53</definedName>
     <definedName function="false" hidden="false" name="ct_AMD8_lo" vbProcedure="false">In!$D$53</definedName>
@@ -271,7 +277,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1302" uniqueCount="846">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1304" uniqueCount="849">
   <si>
     <r>
       <rPr>
@@ -9612,6 +9618,93 @@
     </r>
   </si>
   <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">其他 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">ASIC</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">MTIA</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Maia </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">等）每片封裝數；來源：未找到（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">v0.5 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">補來源欄）</t>
+    </r>
+  </si>
+  <si>
     <t xml:space="preserve">ct_ASIC</t>
   </si>
   <si>
@@ -9837,6 +9930,93 @@
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">用途年增</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">其他 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">CoWoS </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">用途（網通 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">ASIC</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">FPGA</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">、中國 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">AI </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">晶片）年增；來源：未找到</t>
     </r>
   </si>
   <si>
@@ -10255,6 +10435,65 @@
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">年底</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Morgan Stanley 2028 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">年底 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">26 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">萬之後無外部預測：未找到（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">v0.5 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">補來源欄）</t>
     </r>
   </si>
   <si>
@@ -35620,13 +35859,16 @@
       <c r="G62" s="8" t="s">
         <v>43</v>
       </c>
+      <c r="H62" s="4" t="s">
+        <v>177</v>
+      </c>
     </row>
     <row r="63" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="0" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B63" s="0" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C63" s="0" t="s">
         <v>132</v>
@@ -35649,55 +35891,70 @@
     </row>
     <row r="64" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="0" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B64" s="4" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C64" s="4" t="s">
-        <v>181</v>
+        <v>182</v>
+      </c>
+      <c r="D64" s="7" t="n">
+        <v>100</v>
       </c>
       <c r="E64" s="7" t="n">
         <v>150</v>
       </c>
+      <c r="F64" s="7" t="n">
+        <v>200</v>
+      </c>
       <c r="G64" s="8" t="s">
         <v>43</v>
       </c>
       <c r="H64" s="8" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="0" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B65" s="4" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C65" s="0" t="s">
         <v>42</v>
       </c>
+      <c r="D65" s="7" t="n">
+        <v>0.15</v>
+      </c>
       <c r="E65" s="7" t="n">
         <v>0.25</v>
       </c>
+      <c r="F65" s="7" t="n">
+        <v>0.35</v>
+      </c>
       <c r="G65" s="8" t="s">
         <v>43</v>
       </c>
+      <c r="H65" s="4" t="s">
+        <v>186</v>
+      </c>
     </row>
     <row r="66" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="6" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="0" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="B67" s="0" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="C67" s="4" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="E67" s="7" t="n">
         <v>77.5</v>
@@ -35706,18 +35963,18 @@
         <v>33</v>
       </c>
       <c r="H67" s="8" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="0" t="s">
+        <v>192</v>
+      </c>
+      <c r="B68" s="0" t="s">
+        <v>193</v>
+      </c>
+      <c r="C68" s="4" t="s">
         <v>190</v>
-      </c>
-      <c r="B68" s="0" t="s">
-        <v>191</v>
-      </c>
-      <c r="C68" s="4" t="s">
-        <v>188</v>
       </c>
       <c r="E68" s="7" t="n">
         <v>130</v>
@@ -35726,18 +35983,18 @@
         <v>33</v>
       </c>
       <c r="H68" s="8" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="0" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="B69" s="0" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="C69" s="4" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="E69" s="7" t="n">
         <v>200</v>
@@ -35746,18 +36003,18 @@
         <v>33</v>
       </c>
       <c r="H69" s="8" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="0" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="B70" s="0" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="C70" s="4" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="E70" s="7" t="n">
         <v>260</v>
@@ -35766,35 +36023,41 @@
         <v>33</v>
       </c>
       <c r="H70" s="8" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="0" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="B71" s="0" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="C71" s="4" t="s">
-        <v>188</v>
+        <v>190</v>
+      </c>
+      <c r="D71" s="7" t="n">
+        <v>280</v>
       </c>
       <c r="E71" s="7" t="n">
         <v>320</v>
       </c>
+      <c r="F71" s="7" t="n">
+        <v>380</v>
+      </c>
       <c r="G71" s="8" t="s">
         <v>43</v>
       </c>
       <c r="H71" s="8" t="s">
-        <v>43</v>
+        <v>203</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="0" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="B72" s="4" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="C72" s="0" t="s">
         <v>42</v>
@@ -35812,18 +36075,18 @@
         <v>43</v>
       </c>
       <c r="H72" s="4" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="0" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="B73" s="0" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="C73" s="4" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="E73" s="7" t="n">
         <v>1394</v>
@@ -35832,18 +36095,18 @@
         <v>33</v>
       </c>
       <c r="H73" s="8" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="0" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="B74" s="0" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="C74" s="4" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="E74" s="7" t="n">
         <v>2509</v>
@@ -35852,15 +36115,15 @@
         <v>33</v>
       </c>
       <c r="H74" s="8" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="0" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="B75" s="0" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="C75" s="0" t="s">
         <v>42</v>
@@ -35872,23 +36135,23 @@
         <v>128</v>
       </c>
       <c r="H75" s="8" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="6" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="0" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="B77" s="4" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="C77" s="0" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="D77" s="7" t="n">
         <v>30</v>
@@ -35903,98 +36166,98 @@
         <v>43</v>
       </c>
       <c r="H77" s="8" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="0" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="B78" s="4" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="C78" s="0" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="E78" s="7" t="n">
         <v>122.43</v>
       </c>
       <c r="G78" s="8" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="H78" s="4" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="0" t="s">
+        <v>226</v>
+      </c>
+      <c r="B79" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="C79" s="0" t="s">
         <v>223</v>
-      </c>
-      <c r="B79" s="4" t="s">
-        <v>224</v>
-      </c>
-      <c r="C79" s="0" t="s">
-        <v>220</v>
       </c>
       <c r="E79" s="7" t="n">
         <v>35.9</v>
       </c>
       <c r="G79" s="8" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="H79" s="4" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="0" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="B80" s="4" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="C80" s="0" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="E80" s="7" t="n">
         <v>40.2</v>
       </c>
       <c r="G80" s="8" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="H80" s="4" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="0" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="B81" s="4" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="C81" s="0" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="E81" s="7" t="n">
         <v>46.72</v>
       </c>
       <c r="G81" s="8" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="H81" s="4" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="0" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="B82" s="4" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="C82" s="0" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="D82" s="7" t="n">
         <v>52.3</v>
@@ -36009,18 +36272,18 @@
         <v>33</v>
       </c>
       <c r="H82" s="4" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="0" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="B83" s="0" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="C83" s="0" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="E83" s="7" t="n">
         <v>31.8</v>
@@ -36029,78 +36292,78 @@
         <v>33</v>
       </c>
       <c r="H83" s="4" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="0" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="B84" s="4" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="C84" s="0" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="E84" s="7" t="n">
         <v>1134.1</v>
       </c>
       <c r="G84" s="8" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="H84" s="4" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="0" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="B85" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="C85" s="0" t="s">
         <v>243</v>
-      </c>
-      <c r="C85" s="0" t="s">
-        <v>240</v>
       </c>
       <c r="E85" s="7" t="n">
         <v>1270.38</v>
       </c>
       <c r="G85" s="8" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="H85" s="4" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="0" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="B86" s="4" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="C86" s="0" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="E86" s="7" t="n">
         <v>1494.24</v>
       </c>
       <c r="G86" s="8" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="H86" s="4" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="0" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="B87" s="4" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="C87" s="0" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="D87" s="0" t="n">
         <f aca="false">rev26_4q_lo*fx26_4q</f>
@@ -36120,10 +36383,10 @@
     </row>
     <row r="88" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="0" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="B88" s="4" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="C88" s="0" t="s">
         <v>42</v>
@@ -36132,18 +36395,18 @@
         <v>0.662</v>
       </c>
       <c r="G88" s="8" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="H88" s="4" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="0" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="B89" s="4" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="C89" s="0" t="s">
         <v>42</v>
@@ -36152,18 +36415,18 @@
         <v>0.677</v>
       </c>
       <c r="G89" s="8" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="H89" s="4" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="0" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="B90" s="4" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="C90" s="0" t="s">
         <v>42</v>
@@ -36172,18 +36435,18 @@
         <v>0.664</v>
       </c>
       <c r="G90" s="8" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="H90" s="4" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="0" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="B91" s="4" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="C91" s="0" t="s">
         <v>42</v>
@@ -36201,15 +36464,15 @@
         <v>33</v>
       </c>
       <c r="H91" s="4" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="0" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="B92" s="4" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="C92" s="0" t="s">
         <v>42</v>
@@ -36218,18 +36481,18 @@
         <v>0.581</v>
       </c>
       <c r="G92" s="8" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="H92" s="4" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="0" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="B93" s="4" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="C93" s="0" t="s">
         <v>42</v>
@@ -36238,18 +36501,18 @@
         <v>0.603</v>
       </c>
       <c r="G93" s="8" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="H93" s="4" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="0" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="B94" s="4" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="C94" s="0" t="s">
         <v>42</v>
@@ -36258,18 +36521,18 @@
         <v>0.587</v>
       </c>
       <c r="G94" s="8" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="H94" s="4" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="0" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="B95" s="4" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="C95" s="0" t="s">
         <v>42</v>
@@ -36287,96 +36550,96 @@
         <v>33</v>
       </c>
       <c r="H95" s="4" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="0" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="B96" s="4" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="C96" s="0" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="E96" s="7" t="n">
         <v>572.48</v>
       </c>
       <c r="G96" s="8" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="H96" s="4" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="0" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="B97" s="4" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="C97" s="0" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="E97" s="7" t="n">
         <v>706.56</v>
       </c>
       <c r="G97" s="8" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="H97" s="4" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="0" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="B98" s="4" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="C98" s="0" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="E98" s="7" t="n">
         <v>763.06</v>
       </c>
       <c r="G98" s="8" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="H98" s="4" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="0" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="B99" s="0" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="C99" s="0" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="E99" s="0" t="n">
         <f aca="false">22.08+27.25+29.43</f>
         <v>78.76</v>
       </c>
       <c r="G99" s="0" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="H99" s="4" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A100" s="0" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="B100" s="0" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="C100" s="0" t="s">
         <v>42</v>
@@ -36385,18 +36648,18 @@
         <v>0.68</v>
       </c>
       <c r="G100" s="8" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="H100" s="4" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A101" s="0" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="B101" s="4" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="C101" s="0" t="s">
         <v>42</v>
@@ -36408,18 +36671,18 @@
         <v>33</v>
       </c>
       <c r="H101" s="4" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
     </row>
     <row r="102" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A102" s="0" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="B102" s="4" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="C102" s="0" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="D102" s="0" t="n">
         <f aca="false">rev26_1q+rev26_2q+rev26_3q+rev26_4q_lo</f>
@@ -36437,18 +36700,18 @@
         <v>128</v>
       </c>
       <c r="H102" s="0" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
     </row>
     <row r="103" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A103" s="0" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="B103" s="4" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="C103" s="0" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="E103" s="0" t="n">
         <f aca="false">ntd26_1q+ntd26_2q+ntd26_3q+ntd26_4q</f>
@@ -36460,13 +36723,13 @@
     </row>
     <row r="104" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A104" s="0" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="B104" s="0" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="C104" s="0" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="E104" s="0" t="n">
         <f aca="false">ntd26/rev26</f>
@@ -36476,15 +36739,15 @@
         <v>128</v>
       </c>
       <c r="H104" s="4" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
     </row>
     <row r="105" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A105" s="0" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="B105" s="4" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="C105" s="0" t="s">
         <v>42</v>
@@ -36502,15 +36765,15 @@
         <v>43</v>
       </c>
       <c r="H105" s="4" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
     </row>
     <row r="106" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A106" s="0" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="B106" s="0" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="C106" s="0" t="s">
         <v>42</v>
@@ -36519,18 +36782,18 @@
         <v>0.12</v>
       </c>
       <c r="G106" s="8" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="H106" s="8" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
     </row>
     <row r="107" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A107" s="0" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="B107" s="0" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="C107" s="0" t="s">
         <v>42</v>
@@ -36539,7 +36802,7 @@
         <v>0.08</v>
       </c>
       <c r="G107" s="8" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="H107" s="8" t="s">
         <v>43</v>
@@ -36547,10 +36810,10 @@
     </row>
     <row r="108" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A108" s="0" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="B108" s="0" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="C108" s="0" t="s">
         <v>42</v>
@@ -36559,7 +36822,7 @@
         <v>0.05</v>
       </c>
       <c r="G108" s="8" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="H108" s="8" t="s">
         <v>43</v>
@@ -36567,10 +36830,10 @@
     </row>
     <row r="109" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A109" s="0" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="B109" s="4" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="C109" s="0" t="s">
         <v>42</v>
@@ -36582,15 +36845,15 @@
         <v>43</v>
       </c>
       <c r="H109" s="4" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
     </row>
     <row r="110" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A110" s="0" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="B110" s="4" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="C110" s="0" t="s">
         <v>42</v>
@@ -36604,10 +36867,10 @@
     </row>
     <row r="111" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A111" s="0" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="B111" s="4" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="C111" s="0" t="s">
         <v>42</v>
@@ -36621,10 +36884,10 @@
     </row>
     <row r="112" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A112" s="0" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="B112" s="4" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="C112" s="0" t="s">
         <v>42</v>
@@ -36638,10 +36901,10 @@
     </row>
     <row r="113" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A113" s="0" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="B113" s="4" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="C113" s="0" t="s">
         <v>42</v>
@@ -36655,10 +36918,10 @@
     </row>
     <row r="114" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A114" s="0" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="B114" s="4" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="C114" s="0" t="s">
         <v>42</v>
@@ -36672,10 +36935,10 @@
     </row>
     <row r="115" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A115" s="0" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="B115" s="4" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="C115" s="0" t="s">
         <v>42</v>
@@ -36689,10 +36952,10 @@
     </row>
     <row r="116" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A116" s="0" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="B116" s="4" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="C116" s="0" t="s">
         <v>42</v>
@@ -36706,10 +36969,10 @@
     </row>
     <row r="117" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A117" s="0" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="B117" s="4" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="C117" s="0" t="s">
         <v>42</v>
@@ -36723,15 +36986,15 @@
     </row>
     <row r="118" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A118" s="6" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
     </row>
     <row r="119" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A119" s="0" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="B119" s="4" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="C119" s="0" t="s">
         <v>42</v>
@@ -36744,15 +37007,15 @@
         <v>128</v>
       </c>
       <c r="H119" s="0" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
     </row>
     <row r="120" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A120" s="0" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="B120" s="4" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="C120" s="0" t="s">
         <v>42</v>
@@ -36767,10 +37030,10 @@
     </row>
     <row r="121" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A121" s="0" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="B121" s="4" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="C121" s="0" t="s">
         <v>42</v>
@@ -36783,15 +37046,15 @@
         <v>128</v>
       </c>
       <c r="H121" s="4" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
     </row>
     <row r="122" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A122" s="0" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="B122" s="4" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="C122" s="0" t="s">
         <v>112</v>
@@ -36804,15 +37067,15 @@
         <v>128</v>
       </c>
       <c r="H122" s="0" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
     </row>
     <row r="123" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A123" s="0" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="B123" s="4" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="C123" s="0" t="s">
         <v>42</v>
@@ -36824,15 +37087,15 @@
         <v>102</v>
       </c>
       <c r="H123" s="8" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
     </row>
     <row r="124" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A124" s="0" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="B124" s="4" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="C124" s="0" t="s">
         <v>42</v>
@@ -36846,10 +37109,10 @@
     </row>
     <row r="125" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A125" s="0" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="B125" s="4" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="C125" s="0" t="s">
         <v>42</v>
@@ -36863,10 +37126,10 @@
     </row>
     <row r="126" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A126" s="0" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="B126" s="4" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="C126" s="0" t="s">
         <v>42</v>
@@ -36880,10 +37143,10 @@
     </row>
     <row r="127" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A127" s="0" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="B127" s="4" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="C127" s="0" t="s">
         <v>42</v>
@@ -36897,10 +37160,10 @@
     </row>
     <row r="128" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A128" s="0" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="B128" s="4" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="C128" s="0" t="s">
         <v>42</v>
@@ -36914,10 +37177,10 @@
     </row>
     <row r="129" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A129" s="0" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="B129" s="4" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="C129" s="0" t="s">
         <v>42</v>
@@ -36931,10 +37194,10 @@
     </row>
     <row r="130" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A130" s="0" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="B130" s="4" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="C130" s="0" t="s">
         <v>42</v>
@@ -36948,10 +37211,10 @@
     </row>
     <row r="131" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A131" s="0" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="B131" s="4" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="C131" s="0" t="s">
         <v>42</v>
@@ -36965,10 +37228,10 @@
     </row>
     <row r="132" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A132" s="0" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="B132" s="4" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="C132" s="0" t="s">
         <v>42</v>
@@ -36980,15 +37243,15 @@
         <v>128</v>
       </c>
       <c r="H132" s="8" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
     </row>
     <row r="133" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A133" s="0" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="B133" s="4" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="C133" s="0" t="s">
         <v>112</v>
@@ -37009,18 +37272,18 @@
         <v>128</v>
       </c>
       <c r="H133" s="4" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
     </row>
     <row r="134" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A134" s="0" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="B134" s="4" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="C134" s="4" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="E134" s="7" t="n">
         <v>25.93</v>
@@ -37029,38 +37292,38 @@
         <v>128</v>
       </c>
       <c r="H134" s="4" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
     </row>
     <row r="135" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A135" s="0" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="B135" s="4" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="C135" s="0" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="E135" s="7" t="n">
         <v>2385</v>
       </c>
       <c r="G135" s="8" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="H135" s="8" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
     </row>
     <row r="136" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A136" s="0" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="B136" s="4" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="C136" s="0" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="E136" s="7" t="n">
         <v>62</v>
@@ -37069,18 +37332,18 @@
         <v>33</v>
       </c>
       <c r="H136" s="4" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
     </row>
     <row r="137" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A137" s="0" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="B137" s="4" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="C137" s="0" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="E137" s="7" t="n">
         <v>77</v>
@@ -37089,18 +37352,18 @@
         <v>33</v>
       </c>
       <c r="H137" s="8" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
     </row>
     <row r="138" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A138" s="0" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="B138" s="4" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="C138" s="0" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="E138" s="7" t="n">
         <v>90</v>
@@ -37109,18 +37372,18 @@
         <v>33</v>
       </c>
       <c r="H138" s="8" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
     </row>
     <row r="139" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A139" s="0" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="B139" s="4" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="C139" s="0" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="E139" s="7" t="n">
         <v>95</v>
@@ -37131,10 +37394,10 @@
     </row>
     <row r="140" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A140" s="0" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="B140" s="0" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="C140" s="0" t="s">
         <v>112</v>
@@ -37146,15 +37409,15 @@
         <v>33</v>
       </c>
       <c r="H140" s="4" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
     </row>
     <row r="141" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A141" s="0" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="B141" s="0" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="C141" s="0" t="s">
         <v>112</v>
@@ -37166,15 +37429,15 @@
         <v>33</v>
       </c>
       <c r="H141" s="8" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
     </row>
     <row r="142" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A142" s="0" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="B142" s="0" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="C142" s="0" t="s">
         <v>112</v>
@@ -37186,18 +37449,18 @@
         <v>33</v>
       </c>
       <c r="H142" s="8" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
     </row>
     <row r="143" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A143" s="0" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="B143" s="4" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="C143" s="0" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="E143" s="7" t="n">
         <v>229</v>
@@ -37206,18 +37469,18 @@
         <v>33</v>
       </c>
       <c r="H143" s="8" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
     </row>
     <row r="144" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A144" s="0" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="B144" s="4" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="C144" s="0" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="E144" s="7" t="n">
         <v>107.6</v>
@@ -37226,18 +37489,18 @@
         <v>33</v>
       </c>
       <c r="H144" s="8" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
     </row>
     <row r="145" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A145" s="0" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="B145" s="4" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="C145" s="0" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="E145" s="7" t="n">
         <v>142</v>
@@ -37246,15 +37509,15 @@
         <v>33</v>
       </c>
       <c r="H145" s="8" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
     </row>
     <row r="146" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A146" s="0" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="B146" s="0" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="C146" s="0" t="s">
         <v>42</v>
@@ -37263,18 +37526,18 @@
         <v>0.18</v>
       </c>
       <c r="G146" s="8" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="H146" s="4" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
     </row>
     <row r="147" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A147" s="0" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="B147" s="0" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="C147" s="0" t="s">
         <v>42</v>
@@ -37283,18 +37546,18 @@
         <v>0.57</v>
       </c>
       <c r="G147" s="8" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="H147" s="4" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
     </row>
     <row r="148" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A148" s="10" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="B148" s="11" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="C148" s="10" t="s">
         <v>42</v>
@@ -37308,15 +37571,15 @@
         <v>43</v>
       </c>
       <c r="H148" s="10" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
     </row>
     <row r="149" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A149" s="10" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="B149" s="11" t="s">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="C149" s="10" t="s">
         <v>42</v>
@@ -37330,15 +37593,15 @@
         <v>43</v>
       </c>
       <c r="H149" s="10" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
     </row>
     <row r="150" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A150" s="10" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="B150" s="11" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="C150" s="10" t="s">
         <v>42</v>
@@ -37352,15 +37615,15 @@
         <v>43</v>
       </c>
       <c r="H150" s="10" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
     </row>
     <row r="151" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A151" s="10" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="B151" s="11" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="C151" s="10" t="s">
         <v>42</v>
@@ -37374,15 +37637,15 @@
         <v>43</v>
       </c>
       <c r="H151" s="10" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
     </row>
     <row r="152" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A152" s="10" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="B152" s="11" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="C152" s="10" t="s">
         <v>42</v>
@@ -37396,15 +37659,15 @@
         <v>43</v>
       </c>
       <c r="H152" s="10" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
     </row>
     <row r="153" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A153" s="10" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="B153" s="10" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="C153" s="10" t="s">
         <v>42</v>
@@ -37419,15 +37682,15 @@
         <v>128</v>
       </c>
       <c r="H153" s="10" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
     </row>
     <row r="154" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A154" s="10" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="B154" s="11" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="C154" s="10" t="s">
         <v>42</v>
@@ -37441,15 +37704,15 @@
         <v>43</v>
       </c>
       <c r="H154" s="10" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
     </row>
     <row r="155" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A155" s="10" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="B155" s="11" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="C155" s="10" t="s">
         <v>42</v>
@@ -37464,15 +37727,15 @@
         <v>128</v>
       </c>
       <c r="H155" s="10" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
     </row>
     <row r="156" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A156" s="10" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="B156" s="11" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="C156" s="10" t="s">
         <v>42</v>
@@ -37487,15 +37750,15 @@
         <v>43</v>
       </c>
       <c r="H156" s="11" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
     </row>
     <row r="157" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A157" s="10" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="B157" s="11" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="C157" s="10" t="s">
         <v>42</v>
@@ -37510,15 +37773,15 @@
         <v>43</v>
       </c>
       <c r="H157" s="11" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
     </row>
     <row r="158" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A158" s="10" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="B158" s="11" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="C158" s="10" t="s">
         <v>42</v>
@@ -37533,15 +37796,15 @@
         <v>43</v>
       </c>
       <c r="H158" s="11" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
     </row>
     <row r="159" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A159" s="10" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="B159" s="11" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="C159" s="10" t="s">
         <v>42</v>
@@ -37556,15 +37819,15 @@
         <v>128</v>
       </c>
       <c r="H159" s="10" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
     </row>
     <row r="160" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A160" s="10" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="B160" s="11" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="C160" s="10" t="s">
         <v>42</v>
@@ -37579,15 +37842,15 @@
         <v>128</v>
       </c>
       <c r="H160" s="10" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
     </row>
     <row r="161" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A161" s="10" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="B161" s="11" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="C161" s="10" t="s">
         <v>42</v>
@@ -37602,18 +37865,18 @@
         <v>128</v>
       </c>
       <c r="H161" s="10" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
     </row>
     <row r="162" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A162" s="10" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="B162" s="11" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="C162" s="10" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="D162" s="12" t="n">
         <v>2650</v>
@@ -37628,18 +37891,18 @@
         <v>33</v>
       </c>
       <c r="H162" s="10" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
     </row>
     <row r="163" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A163" s="10" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="B163" s="11" t="s">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="C163" s="10" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="D163" s="10"/>
       <c r="E163" s="12" t="n">
@@ -37650,18 +37913,18 @@
         <v>33</v>
       </c>
       <c r="H163" s="10" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
     </row>
     <row r="164" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A164" s="10" t="s">
-        <v>446</v>
+        <v>449</v>
       </c>
       <c r="B164" s="11" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="C164" s="10" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="D164" s="10"/>
       <c r="E164" s="12" t="n">
@@ -37672,15 +37935,15 @@
         <v>33</v>
       </c>
       <c r="H164" s="10" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
     </row>
     <row r="165" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A165" s="0" t="s">
-        <v>449</v>
+        <v>452</v>
       </c>
       <c r="B165" s="4" t="s">
-        <v>450</v>
+        <v>453</v>
       </c>
       <c r="C165" s="0" t="s">
         <v>42</v>
@@ -37693,18 +37956,18 @@
         <v>43</v>
       </c>
       <c r="H165" s="8" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="I165" s="4" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
     </row>
     <row r="166" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A166" s="0" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="B166" s="4" t="s">
-        <v>454</v>
+        <v>457</v>
       </c>
       <c r="C166" s="0" t="s">
         <v>42</v>
@@ -37717,10 +37980,10 @@
         <v>43</v>
       </c>
       <c r="H166" s="8" t="s">
+        <v>458</v>
+      </c>
+      <c r="I166" s="4" t="s">
         <v>455</v>
-      </c>
-      <c r="I166" s="4" t="s">
-        <v>452</v>
       </c>
     </row>
   </sheetData>
@@ -37748,7 +38011,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="0" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -37756,24 +38019,24 @@
         <v>22</v>
       </c>
       <c r="B3" s="15" t="s">
-        <v>457</v>
+        <v>460</v>
       </c>
       <c r="C3" s="15" t="s">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="D3" s="15" t="s">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="E3" s="15" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>461</v>
+        <v>464</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>462</v>
+        <v>465</v>
       </c>
       <c r="B4" s="16" t="n">
         <f aca="false">u_bw_26/pp_GB*1000</f>
@@ -37794,7 +38057,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="3" t="s">
-        <v>463</v>
+        <v>466</v>
       </c>
       <c r="B5" s="16" t="n">
         <f aca="false">u_rb_26/pp_VR*1000</f>
@@ -37815,7 +38078,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="3" t="s">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="B6" s="16" t="n">
         <f aca="false">u_ru_26/pp_RU*1000</f>
@@ -37836,7 +38099,7 @@
     </row>
     <row r="7" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="3" t="s">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="B7" s="16" t="n">
         <f aca="false">u_hp_26/pp_HP*1000</f>
@@ -37857,7 +38120,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="3" t="s">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="B8" s="16" t="n">
         <f aca="false">u_amd_26/pp_AMD8*1000</f>
@@ -37878,7 +38141,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="3" t="s">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="B9" s="16" t="n">
         <f aca="false">u_tpu_26/pp_TPU7*1000</f>
@@ -37899,7 +38162,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="3" t="s">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="B10" s="16" t="n">
         <f aca="false">u_trn_26/pp_TRN*1000</f>
@@ -37920,7 +38183,7 @@
     </row>
     <row r="11" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="2" t="s">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c r="B11" s="16" t="n">
         <f aca="false">u_oth_26/pp_ASIC*1000</f>
@@ -37941,7 +38204,7 @@
     </row>
     <row r="12" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="2" t="s">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="B12" s="16" t="n">
         <f aca="false">cow_oth26</f>
@@ -37962,7 +38225,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="B13" s="16" t="n">
         <f aca="false">SUM(B4:B12)</f>
@@ -37983,7 +38246,7 @@
     </row>
     <row r="14" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="2" t="s">
-        <v>472</v>
+        <v>475</v>
       </c>
       <c r="B14" s="16" t="n">
         <f aca="false">B4+B5+B6+B7</f>
@@ -38004,7 +38267,7 @@
     </row>
     <row r="15" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="2" t="s">
-        <v>473</v>
+        <v>476</v>
       </c>
       <c r="B15" s="16" t="n">
         <f aca="false">(cap_end25+cap_end26)/2*12</f>
@@ -38025,7 +38288,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="2" t="s">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="B16" s="16" t="n">
         <f aca="false">B15*(1+osat)</f>
@@ -38046,7 +38309,7 @@
     </row>
     <row r="17" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="2" t="s">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="B17" s="17" t="n">
         <f aca="false">B13/B16</f>
@@ -38065,24 +38328,24 @@
         <v>0.787180222794447</v>
       </c>
       <c r="F17" s="8" t="s">
-        <v>476</v>
+        <v>479</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="2" t="s">
-        <v>477</v>
+        <v>480</v>
       </c>
       <c r="C18" s="17" t="n">
         <f aca="false">hbm_gap27</f>
         <v>0.21</v>
       </c>
       <c r="F18" s="8" t="s">
-        <v>478</v>
+        <v>481</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="2" t="s">
-        <v>479</v>
+        <v>482</v>
       </c>
       <c r="B19" s="16" t="n">
         <f aca="false">ms_dem26</f>
@@ -38095,7 +38358,7 @@
     </row>
     <row r="20" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="2" t="s">
-        <v>480</v>
+        <v>483</v>
       </c>
       <c r="B20" s="17" t="n">
         <f aca="false">B13/B19-1</f>
@@ -38108,7 +38371,7 @@
     </row>
     <row r="21" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="3" t="s">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="B21" s="17" t="n">
         <f aca="false">B14/660-1</f>
@@ -38145,7 +38408,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="0" t="s">
-        <v>482</v>
+        <v>485</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -38153,66 +38416,66 @@
         <v>22</v>
       </c>
       <c r="B3" s="15" t="s">
-        <v>457</v>
+        <v>460</v>
       </c>
       <c r="C3" s="15" t="s">
-        <v>483</v>
+        <v>486</v>
       </c>
       <c r="D3" s="15" t="s">
-        <v>484</v>
+        <v>487</v>
       </c>
       <c r="E3" s="15" t="s">
-        <v>485</v>
+        <v>488</v>
       </c>
       <c r="F3" s="15" t="s">
-        <v>486</v>
+        <v>489</v>
       </c>
       <c r="G3" s="15" t="s">
-        <v>487</v>
+        <v>490</v>
       </c>
       <c r="H3" s="15" t="s">
-        <v>488</v>
+        <v>491</v>
       </c>
       <c r="I3" s="15" t="s">
-        <v>489</v>
+        <v>492</v>
       </c>
       <c r="J3" s="15" t="s">
-        <v>490</v>
+        <v>493</v>
       </c>
       <c r="K3" s="15" t="s">
-        <v>491</v>
+        <v>494</v>
       </c>
       <c r="L3" s="15" t="s">
-        <v>492</v>
+        <v>495</v>
       </c>
       <c r="M3" s="15" t="s">
-        <v>493</v>
+        <v>496</v>
       </c>
       <c r="N3" s="15" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="O3" s="15" t="s">
-        <v>495</v>
+        <v>498</v>
       </c>
       <c r="P3" s="15" t="s">
-        <v>496</v>
+        <v>499</v>
       </c>
       <c r="Q3" s="15" t="s">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="R3" s="15" t="s">
-        <v>498</v>
+        <v>501</v>
       </c>
       <c r="S3" s="15" t="s">
-        <v>499</v>
+        <v>502</v>
       </c>
       <c r="T3" s="15" t="s">
-        <v>500</v>
+        <v>503</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="0" t="s">
-        <v>501</v>
+        <v>504</v>
       </c>
       <c r="B4" s="18" t="n">
         <f aca="false">(u_bw_26*ct_GB+u_rb_26*ct_VR+u_ru_26*ct_RU+u_hp_26*ct_HP+u_amd_26*ct_AMD8+u_tpu_26*ct_TPU7+u_trn_26*ct_TRN+u_oth_26*ct_ASIC)*1</f>
@@ -38257,7 +38520,7 @@
     </row>
     <row r="5" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="s">
-        <v>502</v>
+        <v>505</v>
       </c>
       <c r="B5" s="18" t="n">
         <f aca="false">B4*(1+ai_oth)</f>
@@ -38302,7 +38565,7 @@
     </row>
     <row r="6" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="4" t="s">
-        <v>503</v>
+        <v>506</v>
       </c>
       <c r="B6" s="18" t="n">
         <f aca="false">B7-B5</f>
@@ -38347,7 +38610,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="4" t="s">
-        <v>504</v>
+        <v>507</v>
       </c>
       <c r="B7" s="18" t="n">
         <f aca="false">rev26</f>
@@ -38428,7 +38691,7 @@
     </row>
     <row r="8" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="0" t="s">
-        <v>505</v>
+        <v>508</v>
       </c>
       <c r="B8" s="14" t="n">
         <f aca="false">B5/B7</f>
@@ -38473,7 +38736,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="4" t="s">
-        <v>506</v>
+        <v>509</v>
       </c>
       <c r="B9" s="14" t="n">
         <f aca="false">gm26</f>
@@ -38518,7 +38781,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="4" t="s">
-        <v>507</v>
+        <v>510</v>
       </c>
       <c r="B10" s="18" t="n">
         <f aca="false">B7*B9</f>
@@ -38563,7 +38826,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="4" t="s">
-        <v>508</v>
+        <v>511</v>
       </c>
       <c r="B11" s="18" t="n">
         <f aca="false">B7*(B9-opex_26)</f>
@@ -38608,7 +38871,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="4" t="s">
-        <v>509</v>
+        <v>512</v>
       </c>
       <c r="B12" s="18" t="n">
         <f aca="false">B11*ni_op_26</f>
@@ -38689,7 +38952,7 @@
     </row>
     <row r="13" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="0" t="s">
-        <v>510</v>
+        <v>513</v>
       </c>
       <c r="B13" s="18" t="n">
         <f aca="false">B12*fx_26/shares</f>
@@ -38770,7 +39033,7 @@
     </row>
     <row r="14" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="4" t="s">
-        <v>511</v>
+        <v>514</v>
       </c>
       <c r="B14" s="20" t="n">
         <f aca="false">px/B13</f>
@@ -38851,7 +39114,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="4" t="s">
-        <v>512</v>
+        <v>515</v>
       </c>
       <c r="B15" s="18" t="n">
         <f aca="false">capex26</f>
@@ -38896,7 +39159,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="4" t="s">
-        <v>513</v>
+        <v>516</v>
       </c>
       <c r="B16" s="18" t="n">
         <f aca="false">B12-B15</f>
@@ -38941,17 +39204,17 @@
     </row>
     <row r="18" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="4" t="s">
-        <v>514</v>
+        <v>517</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="4" t="s">
-        <v>515</v>
+        <v>518</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="4" t="s">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="B20" s="14" t="n">
         <f aca="false">B7/rev25-1</f>
@@ -39032,7 +39295,7 @@
     </row>
     <row r="21" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="4" t="s">
-        <v>517</v>
+        <v>520</v>
       </c>
       <c r="B21" s="14" t="n">
         <f aca="false">B12/B7</f>
@@ -39113,7 +39376,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="4" t="s">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="B22" s="18" t="n">
         <f aca="false">B12+B7*da_rev-B15</f>
@@ -39194,7 +39457,7 @@
     </row>
     <row r="23" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="4" t="s">
-        <v>519</v>
+        <v>522</v>
       </c>
     </row>
   </sheetData>
@@ -39227,45 +39490,45 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="0" t="s">
-        <v>520</v>
+        <v>523</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="5" t="s">
-        <v>521</v>
+        <v>524</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>522</v>
+        <v>525</v>
       </c>
       <c r="C3" s="15" t="s">
-        <v>523</v>
+        <v>526</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>524</v>
+        <v>527</v>
       </c>
       <c r="E3" s="15" t="s">
-        <v>525</v>
+        <v>528</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>526</v>
+        <v>529</v>
       </c>
       <c r="G3" s="5" t="s">
-        <v>527</v>
+        <v>530</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="0" t="s">
-        <v>528</v>
+        <v>531</v>
       </c>
       <c r="B4" s="0" t="n">
         <f aca="false">pe_1</f>
         <v>15</v>
       </c>
       <c r="C4" s="0" t="s">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="D4" s="0" t="s">
-        <v>529</v>
+        <v>532</v>
       </c>
       <c r="E4" s="18" t="n">
         <f aca="false">PL!C13</f>
@@ -39282,17 +39545,17 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="s">
-        <v>528</v>
+        <v>531</v>
       </c>
       <c r="B5" s="0" t="n">
         <f aca="false">pe_2</f>
         <v>20.5</v>
       </c>
       <c r="C5" s="0" t="s">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="D5" s="0" t="s">
-        <v>529</v>
+        <v>532</v>
       </c>
       <c r="E5" s="18" t="n">
         <f aca="false">PL!C13</f>
@@ -39309,17 +39572,17 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="s">
-        <v>528</v>
+        <v>531</v>
       </c>
       <c r="B6" s="0" t="n">
         <f aca="false">pe_3</f>
         <v>32.7</v>
       </c>
       <c r="C6" s="0" t="s">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="D6" s="0" t="s">
-        <v>529</v>
+        <v>532</v>
       </c>
       <c r="E6" s="18" t="n">
         <f aca="false">PL!C13</f>
@@ -39336,17 +39599,17 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="0" t="s">
-        <v>528</v>
+        <v>531</v>
       </c>
       <c r="B7" s="0" t="n">
         <f aca="false">pe_1</f>
         <v>15</v>
       </c>
       <c r="C7" s="0" t="s">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="D7" s="0" t="s">
-        <v>529</v>
+        <v>532</v>
       </c>
       <c r="E7" s="18" t="n">
         <f aca="false">PL!D13</f>
@@ -39363,17 +39626,17 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="0" t="s">
-        <v>528</v>
+        <v>531</v>
       </c>
       <c r="B8" s="0" t="n">
         <f aca="false">pe_2</f>
         <v>20.5</v>
       </c>
       <c r="C8" s="0" t="s">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="D8" s="0" t="s">
-        <v>529</v>
+        <v>532</v>
       </c>
       <c r="E8" s="18" t="n">
         <f aca="false">PL!D13</f>
@@ -39390,17 +39653,17 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="0" t="s">
-        <v>528</v>
+        <v>531</v>
       </c>
       <c r="B9" s="0" t="n">
         <f aca="false">pe_3</f>
         <v>32.7</v>
       </c>
       <c r="C9" s="0" t="s">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="D9" s="0" t="s">
-        <v>529</v>
+        <v>532</v>
       </c>
       <c r="E9" s="18" t="n">
         <f aca="false">PL!D13</f>
@@ -39417,17 +39680,17 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="0" t="s">
-        <v>528</v>
+        <v>531</v>
       </c>
       <c r="B10" s="0" t="n">
         <f aca="false">pe_1</f>
         <v>15</v>
       </c>
       <c r="C10" s="0" t="s">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="D10" s="0" t="s">
-        <v>530</v>
+        <v>533</v>
       </c>
       <c r="E10" s="18" t="n">
         <f aca="false">PL!F13</f>
@@ -39444,17 +39707,17 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="0" t="s">
-        <v>528</v>
+        <v>531</v>
       </c>
       <c r="B11" s="0" t="n">
         <f aca="false">pe_2</f>
         <v>20.5</v>
       </c>
       <c r="C11" s="0" t="s">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="D11" s="0" t="s">
-        <v>530</v>
+        <v>533</v>
       </c>
       <c r="E11" s="18" t="n">
         <f aca="false">PL!F13</f>
@@ -39471,17 +39734,17 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="0" t="s">
-        <v>528</v>
+        <v>531</v>
       </c>
       <c r="B12" s="0" t="n">
         <f aca="false">pe_3</f>
         <v>32.7</v>
       </c>
       <c r="C12" s="0" t="s">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="D12" s="0" t="s">
-        <v>530</v>
+        <v>533</v>
       </c>
       <c r="E12" s="18" t="n">
         <f aca="false">PL!F13</f>
@@ -39498,17 +39761,17 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="0" t="s">
-        <v>528</v>
+        <v>531</v>
       </c>
       <c r="B13" s="0" t="n">
         <f aca="false">pe_1</f>
         <v>15</v>
       </c>
       <c r="C13" s="0" t="s">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="D13" s="0" t="s">
-        <v>530</v>
+        <v>533</v>
       </c>
       <c r="E13" s="18" t="n">
         <f aca="false">PL!G13</f>
@@ -39525,17 +39788,17 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="0" t="s">
-        <v>528</v>
+        <v>531</v>
       </c>
       <c r="B14" s="0" t="n">
         <f aca="false">pe_2</f>
         <v>20.5</v>
       </c>
       <c r="C14" s="0" t="s">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="D14" s="0" t="s">
-        <v>530</v>
+        <v>533</v>
       </c>
       <c r="E14" s="18" t="n">
         <f aca="false">PL!G13</f>
@@ -39552,17 +39815,17 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="0" t="s">
-        <v>528</v>
+        <v>531</v>
       </c>
       <c r="B15" s="0" t="n">
         <f aca="false">pe_3</f>
         <v>32.7</v>
       </c>
       <c r="C15" s="0" t="s">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="D15" s="0" t="s">
-        <v>530</v>
+        <v>533</v>
       </c>
       <c r="E15" s="18" t="n">
         <f aca="false">PL!G13</f>
@@ -39579,17 +39842,17 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="0" t="s">
-        <v>528</v>
+        <v>531</v>
       </c>
       <c r="B16" s="0" t="n">
         <f aca="false">pe_1</f>
         <v>15</v>
       </c>
       <c r="C16" s="0" t="s">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="D16" s="0" t="s">
-        <v>531</v>
+        <v>534</v>
       </c>
       <c r="E16" s="18" t="n">
         <f aca="false">PL!I13</f>
@@ -39606,17 +39869,17 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="0" t="s">
-        <v>528</v>
+        <v>531</v>
       </c>
       <c r="B17" s="0" t="n">
         <f aca="false">pe_2</f>
         <v>20.5</v>
       </c>
       <c r="C17" s="0" t="s">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="D17" s="0" t="s">
-        <v>531</v>
+        <v>534</v>
       </c>
       <c r="E17" s="18" t="n">
         <f aca="false">PL!I13</f>
@@ -39633,17 +39896,17 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="0" t="s">
-        <v>528</v>
+        <v>531</v>
       </c>
       <c r="B18" s="0" t="n">
         <f aca="false">pe_3</f>
         <v>32.7</v>
       </c>
       <c r="C18" s="0" t="s">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="D18" s="0" t="s">
-        <v>531</v>
+        <v>534</v>
       </c>
       <c r="E18" s="18" t="n">
         <f aca="false">PL!I13</f>
@@ -39660,17 +39923,17 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="0" t="s">
-        <v>528</v>
+        <v>531</v>
       </c>
       <c r="B19" s="0" t="n">
         <f aca="false">pe_1</f>
         <v>15</v>
       </c>
       <c r="C19" s="0" t="s">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="D19" s="0" t="s">
-        <v>531</v>
+        <v>534</v>
       </c>
       <c r="E19" s="18" t="n">
         <f aca="false">PL!J13</f>
@@ -39687,17 +39950,17 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="0" t="s">
-        <v>528</v>
+        <v>531</v>
       </c>
       <c r="B20" s="0" t="n">
         <f aca="false">pe_2</f>
         <v>20.5</v>
       </c>
       <c r="C20" s="0" t="s">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="D20" s="0" t="s">
-        <v>531</v>
+        <v>534</v>
       </c>
       <c r="E20" s="18" t="n">
         <f aca="false">PL!J13</f>
@@ -39714,17 +39977,17 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="0" t="s">
-        <v>528</v>
+        <v>531</v>
       </c>
       <c r="B21" s="0" t="n">
         <f aca="false">pe_3</f>
         <v>32.7</v>
       </c>
       <c r="C21" s="0" t="s">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="D21" s="0" t="s">
-        <v>531</v>
+        <v>534</v>
       </c>
       <c r="E21" s="18" t="n">
         <f aca="false">PL!J13</f>
@@ -39741,41 +40004,41 @@
     </row>
     <row r="23" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="4" t="s">
-        <v>532</v>
+        <v>535</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="6" t="s">
-        <v>533</v>
+        <v>536</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="4" t="s">
-        <v>534</v>
+        <v>537</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="6" t="s">
-        <v>535</v>
+        <v>538</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="5" t="s">
-        <v>536</v>
+        <v>539</v>
       </c>
       <c r="B30" s="15" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
       <c r="C30" s="15" t="s">
-        <v>538</v>
+        <v>541</v>
       </c>
       <c r="D30" s="5" t="s">
-        <v>539</v>
+        <v>542</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="0" t="s">
-        <v>540</v>
+        <v>543</v>
       </c>
       <c r="B31" s="23" t="n">
         <v>14.5</v>
@@ -39784,12 +40047,12 @@
         <v>11.6</v>
       </c>
       <c r="D31" s="8" t="s">
-        <v>541</v>
+        <v>544</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="0" t="s">
-        <v>542</v>
+        <v>545</v>
       </c>
       <c r="B32" s="23" t="n">
         <v>17.71</v>
@@ -39800,7 +40063,7 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="0" t="s">
-        <v>543</v>
+        <v>546</v>
       </c>
       <c r="B33" s="23" t="n">
         <v>16.13</v>
@@ -39811,7 +40074,7 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="0" t="s">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="B34" s="23" t="n">
         <v>25.62</v>
@@ -39822,7 +40085,7 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="0" t="s">
-        <v>545</v>
+        <v>548</v>
       </c>
       <c r="B35" s="23" t="n">
         <v>31.11</v>
@@ -39833,7 +40096,7 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="0" t="s">
-        <v>546</v>
+        <v>549</v>
       </c>
       <c r="B36" s="23" t="n">
         <v>29.18</v>
@@ -39844,7 +40107,7 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="0" t="s">
-        <v>547</v>
+        <v>550</v>
       </c>
       <c r="B37" s="23" t="n">
         <v>11.94</v>
@@ -39855,7 +40118,7 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="0" t="s">
-        <v>548</v>
+        <v>551</v>
       </c>
       <c r="B38" s="23" t="n">
         <v>19.46</v>
@@ -39866,7 +40129,7 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="0" t="s">
-        <v>549</v>
+        <v>552</v>
       </c>
       <c r="B39" s="23" t="n">
         <v>28.72</v>
@@ -39877,7 +40140,7 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="0" t="s">
-        <v>550</v>
+        <v>553</v>
       </c>
       <c r="B40" s="23" t="n">
         <v>29.03</v>
@@ -39888,7 +40151,7 @@
     </row>
     <row r="41" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="0" t="s">
-        <v>551</v>
+        <v>554</v>
       </c>
       <c r="B41" s="24" t="n">
         <f aca="false">PERCENTILE(B31:B40,0.25)</f>
@@ -39901,7 +40164,7 @@
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="4" t="s">
-        <v>552</v>
+        <v>555</v>
       </c>
       <c r="B42" s="24" t="n">
         <f aca="false">MEDIAN(B31:B40)</f>
@@ -39914,7 +40177,7 @@
     </row>
     <row r="43" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="0" t="s">
-        <v>553</v>
+        <v>556</v>
       </c>
       <c r="B43" s="24" t="n">
         <f aca="false">PERCENTILE(B31:B40,0.75)</f>
@@ -39927,7 +40190,7 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="4" t="s">
-        <v>554</v>
+        <v>557</v>
       </c>
       <c r="B44" s="24" t="n">
         <f aca="false">MIN(B31:B40)</f>
@@ -39940,7 +40203,7 @@
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="4" t="s">
-        <v>555</v>
+        <v>558</v>
       </c>
       <c r="B45" s="24" t="n">
         <f aca="false">MAX(B31:B40)</f>
@@ -39953,7 +40216,7 @@
     </row>
     <row r="46" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="1" t="s">
-        <v>556</v>
+        <v>559</v>
       </c>
       <c r="B46" s="24" t="n">
         <f aca="false">ROUND(AVERAGE(B41,C41),2)</f>
@@ -39962,7 +40225,7 @@
     </row>
     <row r="47" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="1" t="s">
-        <v>557</v>
+        <v>560</v>
       </c>
       <c r="B47" s="24" t="n">
         <f aca="false">ROUND(AVERAGE(B42,C42),2)</f>
@@ -39971,7 +40234,7 @@
     </row>
     <row r="48" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="1" t="s">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="B48" s="24" t="n">
         <f aca="false">ROUND(AVERAGE(B43,C43),2)</f>
@@ -39980,7 +40243,7 @@
     </row>
     <row r="49" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="1" t="s">
-        <v>559</v>
+        <v>562</v>
       </c>
       <c r="B49" s="24" t="n">
         <f aca="false">ROUND(MIN(B44,C44),2)</f>
@@ -39989,7 +40252,7 @@
     </row>
     <row r="50" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="1" t="s">
-        <v>560</v>
+        <v>563</v>
       </c>
       <c r="B50" s="24" t="n">
         <f aca="false">ROUND(MAX(B45,C45),2)</f>
@@ -39998,48 +40261,48 @@
     </row>
     <row r="52" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="6" t="s">
-        <v>561</v>
+        <v>564</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="5" t="s">
-        <v>562</v>
+        <v>565</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>563</v>
+        <v>566</v>
       </c>
       <c r="C53" s="5" t="s">
-        <v>522</v>
+        <v>525</v>
       </c>
       <c r="D53" s="5" t="s">
         <v>25</v>
       </c>
       <c r="E53" s="5" t="s">
-        <v>564</v>
+        <v>567</v>
       </c>
       <c r="F53" s="5" t="s">
-        <v>526</v>
+        <v>529</v>
       </c>
       <c r="G53" s="5" t="s">
-        <v>527</v>
+        <v>530</v>
       </c>
       <c r="H53" s="5" t="s">
-        <v>565</v>
+        <v>568</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="4" t="s">
-        <v>566</v>
+        <v>569</v>
       </c>
       <c r="B54" s="4" t="s">
-        <v>567</v>
+        <v>570</v>
       </c>
       <c r="C54" s="24" t="n">
         <f aca="false">B47</f>
         <v>21.97</v>
       </c>
       <c r="D54" s="8" t="s">
-        <v>568</v>
+        <v>571</v>
       </c>
       <c r="E54" s="18" t="n">
         <f aca="false">PL!C13</f>
@@ -40060,17 +40323,17 @@
     </row>
     <row r="55" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="4" t="s">
-        <v>569</v>
+        <v>572</v>
       </c>
       <c r="B55" s="0" t="s">
-        <v>570</v>
+        <v>573</v>
       </c>
       <c r="C55" s="24" t="n">
         <f aca="false">B46</f>
         <v>15.44</v>
       </c>
       <c r="D55" s="8" t="s">
-        <v>568</v>
+        <v>571</v>
       </c>
       <c r="E55" s="18" t="n">
         <f aca="false">PL!C13</f>
@@ -40091,17 +40354,17 @@
     </row>
     <row r="56" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="4" t="s">
-        <v>571</v>
+        <v>574</v>
       </c>
       <c r="B56" s="0" t="s">
-        <v>572</v>
+        <v>575</v>
       </c>
       <c r="C56" s="24" t="n">
         <f aca="false">B48</f>
         <v>28.49</v>
       </c>
       <c r="D56" s="8" t="s">
-        <v>568</v>
+        <v>571</v>
       </c>
       <c r="E56" s="18" t="n">
         <f aca="false">PL!C13</f>
@@ -40122,17 +40385,17 @@
     </row>
     <row r="57" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="4" t="s">
-        <v>573</v>
+        <v>576</v>
       </c>
       <c r="B57" s="4" t="s">
-        <v>574</v>
+        <v>577</v>
       </c>
       <c r="C57" s="24" t="n">
         <f aca="false">B48</f>
         <v>28.49</v>
       </c>
       <c r="D57" s="8" t="s">
-        <v>575</v>
+        <v>578</v>
       </c>
       <c r="E57" s="18" t="n">
         <f aca="false">PL!J13</f>
@@ -40153,12 +40416,12 @@
     </row>
     <row r="59" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="6" t="s">
-        <v>576</v>
+        <v>579</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="6" t="s">
-        <v>577</v>
+        <v>580</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -40166,29 +40429,29 @@
         <v>22</v>
       </c>
       <c r="B61" s="15" t="s">
-        <v>578</v>
+        <v>581</v>
       </c>
       <c r="C61" s="15" t="s">
-        <v>579</v>
+        <v>582</v>
       </c>
       <c r="D61" s="15" t="s">
-        <v>580</v>
+        <v>583</v>
       </c>
       <c r="E61" s="5" t="s">
-        <v>461</v>
+        <v>464</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="4" t="s">
-        <v>581</v>
+        <v>584</v>
       </c>
       <c r="E62" s="0" t="s">
-        <v>582</v>
+        <v>585</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="0" t="s">
-        <v>583</v>
+        <v>586</v>
       </c>
       <c r="B63" s="24" t="n">
         <f aca="false">PL!C13</f>
@@ -40205,7 +40468,7 @@
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="0" t="s">
-        <v>584</v>
+        <v>587</v>
       </c>
       <c r="B64" s="24" t="n">
         <f aca="false">PL!D13</f>
@@ -40222,7 +40485,7 @@
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="0" t="s">
-        <v>585</v>
+        <v>588</v>
       </c>
       <c r="B65" s="24" t="n">
         <f aca="false">PL!E13</f>
@@ -40239,7 +40502,7 @@
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="0" t="s">
-        <v>586</v>
+        <v>589</v>
       </c>
       <c r="B66" s="24" t="n">
         <f aca="false">PL!L13</f>
@@ -40256,7 +40519,7 @@
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="0" t="s">
-        <v>587</v>
+        <v>590</v>
       </c>
       <c r="B67" s="24" t="n">
         <f aca="false">PL!M13</f>
@@ -40273,7 +40536,7 @@
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="0" t="s">
-        <v>588</v>
+        <v>591</v>
       </c>
       <c r="B68" s="24" t="n">
         <f aca="false">PL!N13</f>
@@ -40290,27 +40553,27 @@
     </row>
     <row r="69" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="4" t="s">
-        <v>589</v>
+        <v>592</v>
       </c>
       <c r="E69" s="4" t="s">
-        <v>590</v>
+        <v>593</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="4" t="s">
-        <v>591</v>
+        <v>594</v>
       </c>
       <c r="B70" s="14" t="n">
         <f aca="false">MIN(tp_g/tp_roe,0.8)</f>
         <v>0.130875777074926</v>
       </c>
       <c r="E70" s="8" t="s">
-        <v>592</v>
+        <v>595</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="0" t="s">
-        <v>583</v>
+        <v>586</v>
       </c>
       <c r="B71" s="24" t="n">
         <f aca="false">B63*(1-$B$70)</f>
@@ -40327,7 +40590,7 @@
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="0" t="s">
-        <v>584</v>
+        <v>587</v>
       </c>
       <c r="B72" s="24" t="n">
         <f aca="false">B64*(1-$B$70)</f>
@@ -40344,7 +40607,7 @@
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="0" t="s">
-        <v>585</v>
+        <v>588</v>
       </c>
       <c r="B73" s="24" t="n">
         <f aca="false">B65*(1-$B$70)</f>
@@ -40361,7 +40624,7 @@
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="0" t="s">
-        <v>586</v>
+        <v>589</v>
       </c>
       <c r="B74" s="24" t="n">
         <f aca="false">B66*(1-$B$70)</f>
@@ -40378,7 +40641,7 @@
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="0" t="s">
-        <v>587</v>
+        <v>590</v>
       </c>
       <c r="B75" s="24" t="n">
         <f aca="false">B67*(1-$B$70)</f>
@@ -40395,7 +40658,7 @@
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="0" t="s">
-        <v>588</v>
+        <v>591</v>
       </c>
       <c r="B76" s="24" t="n">
         <f aca="false">B68*(1-$B$70)</f>
@@ -40412,7 +40675,7 @@
     </row>
     <row r="77" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="0" t="s">
-        <v>593</v>
+        <v>596</v>
       </c>
       <c r="B77" s="16" t="n">
         <f aca="false">SUMPRODUCT(B71:B76,1/(1+tp_r)^{1;2;3;4;5;6})+B76*(1+tp_g)/(tp_r-tp_g)/(1+tp_r)^6</f>
@@ -40427,12 +40690,12 @@
         <v>1359.89907002946</v>
       </c>
       <c r="E77" s="8" t="s">
-        <v>594</v>
+        <v>597</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="0" t="s">
-        <v>595</v>
+        <v>598</v>
       </c>
       <c r="B78" s="16" t="n">
         <f aca="false">B77*(1+tp_r)</f>
@@ -40449,36 +40712,36 @@
     </row>
     <row r="79" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="0" t="s">
-        <v>596</v>
+        <v>599</v>
       </c>
       <c r="B79" s="26" t="n">
         <f aca="false">tp_wA*B78+tp_wB*C78+tp_wC*D78</f>
         <v>2150.17798362528</v>
       </c>
       <c r="E79" s="8" t="s">
-        <v>597</v>
+        <v>600</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="6" t="s">
-        <v>598</v>
+        <v>601</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="5" t="s">
-        <v>599</v>
+        <v>602</v>
       </c>
       <c r="B82" s="5" t="s">
-        <v>600</v>
+        <v>603</v>
       </c>
       <c r="C82" s="5" t="s">
-        <v>601</v>
+        <v>604</v>
       </c>
       <c r="D82" s="5" t="s">
-        <v>602</v>
+        <v>605</v>
       </c>
       <c r="E82" s="5" t="s">
-        <v>603</v>
+        <v>606</v>
       </c>
       <c r="F82" s="5" t="s">
         <v>27</v>
@@ -40486,19 +40749,19 @@
     </row>
     <row r="83" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="4" t="s">
-        <v>604</v>
+        <v>607</v>
       </c>
       <c r="B83" s="0" t="s">
-        <v>605</v>
+        <v>608</v>
       </c>
       <c r="C83" s="27" t="n">
         <v>20.46</v>
       </c>
       <c r="D83" s="8" t="s">
-        <v>606</v>
+        <v>609</v>
       </c>
       <c r="E83" s="8" t="s">
-        <v>607</v>
+        <v>610</v>
       </c>
       <c r="F83" s="8" t="s">
         <v>33</v>
@@ -40506,19 +40769,19 @@
     </row>
     <row r="84" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="4" t="s">
-        <v>608</v>
+        <v>611</v>
       </c>
       <c r="B84" s="0" t="s">
-        <v>609</v>
+        <v>612</v>
       </c>
       <c r="C84" s="27" t="n">
         <v>20.04</v>
       </c>
       <c r="D84" s="8" t="s">
+        <v>613</v>
+      </c>
+      <c r="E84" s="8" t="s">
         <v>610</v>
-      </c>
-      <c r="E84" s="8" t="s">
-        <v>607</v>
       </c>
       <c r="F84" s="8" t="s">
         <v>33</v>
@@ -40526,19 +40789,19 @@
     </row>
     <row r="85" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="4" t="s">
-        <v>611</v>
+        <v>614</v>
       </c>
       <c r="B85" s="0" t="s">
-        <v>612</v>
+        <v>615</v>
       </c>
       <c r="C85" s="27" t="n">
         <v>50.64</v>
       </c>
       <c r="D85" s="8" t="s">
-        <v>606</v>
+        <v>609</v>
       </c>
       <c r="E85" s="8" t="s">
-        <v>607</v>
+        <v>610</v>
       </c>
       <c r="F85" s="8" t="s">
         <v>33</v>
@@ -40546,19 +40809,19 @@
     </row>
     <row r="86" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="4" t="s">
-        <v>613</v>
+        <v>616</v>
       </c>
       <c r="B86" s="0" t="s">
-        <v>614</v>
+        <v>617</v>
       </c>
       <c r="C86" s="27" t="n">
         <v>37.14</v>
       </c>
       <c r="D86" s="8" t="s">
-        <v>615</v>
+        <v>618</v>
       </c>
       <c r="E86" s="8" t="s">
-        <v>607</v>
+        <v>610</v>
       </c>
       <c r="F86" s="8" t="s">
         <v>33</v>
@@ -40566,19 +40829,19 @@
     </row>
     <row r="87" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="4" t="s">
-        <v>616</v>
+        <v>619</v>
       </c>
       <c r="B87" s="0" t="s">
-        <v>617</v>
+        <v>620</v>
       </c>
       <c r="C87" s="27" t="n">
         <v>3.35</v>
       </c>
       <c r="D87" s="8" t="s">
-        <v>618</v>
+        <v>621</v>
       </c>
       <c r="E87" s="8" t="s">
-        <v>607</v>
+        <v>610</v>
       </c>
       <c r="F87" s="8" t="s">
         <v>33</v>
@@ -40586,43 +40849,43 @@
     </row>
     <row r="88" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="4" t="s">
-        <v>619</v>
+        <v>622</v>
       </c>
       <c r="B88" s="18" t="n">
         <f aca="false">MEDIAN(C83:C87)</f>
         <v>20.46</v>
       </c>
       <c r="E88" s="4" t="s">
-        <v>620</v>
+        <v>623</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="0" t="s">
-        <v>621</v>
+        <v>624</v>
       </c>
       <c r="B89" s="24" t="n">
         <f aca="false">tp_wA*(2/12*B63+10/12*B64)+tp_wB*(2/12*C63+10/12*C64)+tp_wC*(2/12*D63+10/12*D64)</f>
         <v>134.011173721684</v>
       </c>
       <c r="E89" s="4" t="s">
-        <v>622</v>
+        <v>625</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="0" t="s">
-        <v>623</v>
+        <v>626</v>
       </c>
       <c r="B90" s="26" t="n">
         <f aca="false">B88*B89</f>
         <v>2741.86861434566</v>
       </c>
       <c r="E90" s="4" t="s">
-        <v>624</v>
+        <v>627</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="6" t="s">
-        <v>625</v>
+        <v>628</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -40630,29 +40893,29 @@
         <v>22</v>
       </c>
       <c r="B93" s="5" t="s">
-        <v>626</v>
+        <v>629</v>
       </c>
       <c r="C93" s="5"/>
       <c r="D93" s="5"/>
       <c r="E93" s="5" t="s">
-        <v>461</v>
+        <v>464</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="4" t="s">
-        <v>627</v>
+        <v>630</v>
       </c>
       <c r="B94" s="26" t="n">
         <f aca="false">tp_w_dcf*B79+(1-tp_w_dcf)*B90</f>
         <v>2446.02329898547</v>
       </c>
       <c r="E94" s="8" t="s">
-        <v>628</v>
+        <v>631</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="0" t="s">
-        <v>629</v>
+        <v>632</v>
       </c>
       <c r="B95" s="16" t="n">
         <f aca="false">B90</f>
@@ -40661,31 +40924,31 @@
     </row>
     <row r="96" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="4" t="s">
-        <v>630</v>
+        <v>633</v>
       </c>
       <c r="B96" s="16" t="n">
         <f aca="false">cons_tp</f>
         <v>3390.43</v>
       </c>
       <c r="E96" s="8" t="s">
-        <v>631</v>
+        <v>634</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="4" t="s">
-        <v>632</v>
+        <v>635</v>
       </c>
       <c r="B97" s="14" t="n">
         <f aca="false">B94/px-1</f>
         <v>0.0255862888827967</v>
       </c>
       <c r="E97" s="4" t="s">
-        <v>633</v>
+        <v>636</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="4" t="s">
-        <v>634</v>
+        <v>637</v>
       </c>
       <c r="B98" s="14" t="n">
         <f aca="false">B95/px-1</f>
@@ -40694,19 +40957,19 @@
     </row>
     <row r="99" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="4" t="s">
-        <v>635</v>
+        <v>638</v>
       </c>
       <c r="B99" s="14" t="n">
         <f aca="false">B89/(2/12*cons_feps27+10/12*cons_feps28)-1</f>
         <v>-0.261714220613254</v>
       </c>
       <c r="E99" s="4" t="s">
-        <v>636</v>
+        <v>639</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A100" s="4" t="s">
-        <v>637</v>
+        <v>640</v>
       </c>
       <c r="B100" s="14" t="n">
         <f aca="false">(cons_tp/(2/12*cons_feps27+10/12*cons_feps28))/B88-1</f>
@@ -40719,19 +40982,19 @@
     </row>
     <row r="101" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A101" s="4" t="s">
-        <v>638</v>
+        <v>641</v>
       </c>
       <c r="B101" s="28" t="str">
         <f aca="false">TEXT(D78,"#,##0")&amp;"～"&amp;TEXT(B78,"#,##0")</f>
         <v>1,496～2,769</v>
       </c>
       <c r="E101" s="8" t="s">
-        <v>639</v>
+        <v>642</v>
       </c>
     </row>
     <row r="102" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A102" s="4" t="s">
-        <v>640</v>
+        <v>643</v>
       </c>
       <c r="B102" s="17" t="n">
         <f aca="false">IF(px/B64&gt;=MAX($C$31:$C$40),1,IF(px/B64&lt;=MIN($C$31:$C$40),0,PERCENTRANK($C$31:$C$40,px/B64)))</f>
@@ -40746,20 +41009,20 @@
         <v>0.527</v>
       </c>
       <c r="E102" s="4" t="s">
-        <v>641</v>
+        <v>644</v>
       </c>
     </row>
     <row r="103" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A103" s="4" t="s">
-        <v>642</v>
+        <v>645</v>
       </c>
       <c r="B103" s="0" t="s">
-        <v>643</v>
+        <v>646</v>
       </c>
     </row>
     <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A105" s="1" t="s">
-        <v>644</v>
+        <v>647</v>
       </c>
     </row>
     <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -40767,29 +41030,29 @@
         <v>22</v>
       </c>
       <c r="B106" s="5" t="s">
-        <v>626</v>
+        <v>629</v>
       </c>
       <c r="C106" s="5"/>
       <c r="D106" s="5"/>
       <c r="E106" s="5" t="s">
-        <v>461</v>
+        <v>464</v>
       </c>
     </row>
     <row r="107" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A107" s="4" t="s">
-        <v>645</v>
+        <v>648</v>
       </c>
       <c r="B107" s="16" t="n">
         <f aca="false">tp_wA*B109+tp_wB*B110+tp_wC*B111</f>
         <v>3022.97680876707</v>
       </c>
       <c r="E107" s="4" t="s">
-        <v>646</v>
+        <v>649</v>
       </c>
     </row>
     <row r="108" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A108" s="4" t="s">
-        <v>647</v>
+        <v>650</v>
       </c>
       <c r="B108" s="14" t="n">
         <f aca="false">B107/px-1</f>
@@ -40798,43 +41061,43 @@
     </row>
     <row r="109" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A109" s="4" t="s">
-        <v>648</v>
+        <v>651</v>
       </c>
       <c r="B109" s="16" t="n">
         <f aca="false">$C$54*PL!C13</f>
         <v>3022.97680876707</v>
       </c>
       <c r="E109" s="4" t="s">
-        <v>649</v>
+        <v>652</v>
       </c>
     </row>
     <row r="110" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A110" s="4" t="s">
-        <v>650</v>
+        <v>653</v>
       </c>
       <c r="B110" s="16" t="n">
         <f aca="false">$C$54*PL!F13</f>
         <v>3022.97680876707</v>
       </c>
       <c r="E110" s="4" t="s">
-        <v>651</v>
+        <v>654</v>
       </c>
     </row>
     <row r="111" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A111" s="4" t="s">
-        <v>652</v>
+        <v>655</v>
       </c>
       <c r="B111" s="16" t="n">
         <f aca="false">$C$54*PL!I13</f>
         <v>3022.97680876707</v>
       </c>
       <c r="E111" s="4" t="s">
-        <v>653</v>
+        <v>656</v>
       </c>
     </row>
     <row r="112" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A112" s="4" t="s">
-        <v>654</v>
+        <v>657</v>
       </c>
       <c r="B112" s="17" t="n">
         <f aca="false">tp_wA</f>
@@ -40855,34 +41118,34 @@
     </row>
     <row r="113" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A113" s="4" t="s">
-        <v>655</v>
+        <v>658</v>
       </c>
       <c r="B113" s="4" t="s">
-        <v>656</v>
+        <v>659</v>
       </c>
     </row>
     <row r="115" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A115" s="4" t="s">
-        <v>657</v>
+        <v>660</v>
       </c>
       <c r="B115" s="28" t="str">
         <f aca="false">IF(B97&gt;0.5,"大於 50%",IF(B97&gt;0.25,"25%–50%",IF(B97&gt;=0,"0%–25%",IF(B97&gt;=-0.25,"0%～−25%",IF(B97&gt;=-0.5,"−25%～−50%","小於 −50%")))))</f>
         <v>0%–25%</v>
       </c>
       <c r="E115" s="4" t="s">
-        <v>658</v>
+        <v>661</v>
       </c>
     </row>
     <row r="116" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A116" s="4" t="s">
-        <v>659</v>
+        <v>662</v>
       </c>
       <c r="B116" s="28" t="str">
         <f aca="false">IF(B97&gt;0.5,"強力買進",IF(B97&gt;0.25,"買進",IF(B97&gt;=-0.25,"中立",IF(B97&gt;=-0.5,"放空","強力放空"))))</f>
         <v>中立</v>
       </c>
       <c r="E116" s="4" t="s">
-        <v>660</v>
+        <v>663</v>
       </c>
     </row>
   </sheetData>
@@ -40910,7 +41173,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="0" t="s">
-        <v>661</v>
+        <v>664</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -40918,21 +41181,21 @@
         <v>22</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>662</v>
+        <v>665</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>663</v>
+        <v>666</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>664</v>
+        <v>667</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>665</v>
+        <v>668</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="0" t="s">
-        <v>666</v>
+        <v>669</v>
       </c>
       <c r="B4" s="25" t="n">
         <f aca="false">PL!B5</f>
@@ -40947,12 +41210,12 @@
         <v>-0.00788231517711135</v>
       </c>
       <c r="E4" s="8" t="s">
-        <v>667</v>
+        <v>670</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="s">
-        <v>668</v>
+        <v>671</v>
       </c>
       <c r="B5" s="25" t="n">
         <f aca="false">PL!B4</f>
@@ -40967,12 +41230,12 @@
         <v>-0.173235262647593</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>669</v>
+        <v>672</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="s">
-        <v>670</v>
+        <v>673</v>
       </c>
       <c r="B6" s="25" t="n">
         <f aca="false">PL!B13</f>
@@ -40987,12 +41250,12 @@
         <v>0.0417778779533982</v>
       </c>
       <c r="E6" s="8" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="0" t="s">
-        <v>671</v>
+        <v>674</v>
       </c>
       <c r="B7" s="25" t="n">
         <f aca="false">PL!B7</f>
@@ -41007,12 +41270,12 @@
         <v>-0.00101645384664262</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>672</v>
+        <v>675</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="0" t="s">
-        <v>673</v>
+        <v>676</v>
       </c>
       <c r="B8" s="25" t="n">
         <f aca="false">PL!B13</f>
@@ -41027,12 +41290,12 @@
         <v>-5.0502654148521E-005</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>674</v>
+        <v>677</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="0" t="s">
-        <v>675</v>
+        <v>678</v>
       </c>
       <c r="B9" s="25" t="n">
         <f aca="false">PL!C7</f>
@@ -41047,12 +41310,12 @@
         <v>-0.0147032314410479</v>
       </c>
       <c r="E9" s="8" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="0" t="s">
-        <v>676</v>
+        <v>679</v>
       </c>
       <c r="B10" s="25" t="n">
         <f aca="false">PL!C13</f>
@@ -41067,12 +41330,12 @@
         <v>-0.0310164280462261</v>
       </c>
       <c r="E10" s="8" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="0" t="s">
-        <v>677</v>
+        <v>680</v>
       </c>
       <c r="B11" s="25" t="n">
         <f aca="false">CoWoS!B13</f>
@@ -41087,12 +41350,12 @@
         <v>-0.205267126392436</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="0" t="s">
-        <v>678</v>
+        <v>681</v>
       </c>
       <c r="B12" s="25" t="n">
         <f aca="false">CoWoS!C13</f>
@@ -41107,12 +41370,12 @@
         <v>-0.16443659966976</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="0" t="s">
-        <v>679</v>
+        <v>682</v>
       </c>
       <c r="B13" s="25" t="n">
         <f aca="false">PL!C13</f>
@@ -41127,12 +41390,12 @@
         <v>-0.0709272976540452</v>
       </c>
       <c r="E13" s="8" t="s">
-        <v>680</v>
+        <v>683</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="0" t="s">
-        <v>681</v>
+        <v>684</v>
       </c>
       <c r="B14" s="25" t="n">
         <f aca="false">PL!D13</f>
@@ -41147,7 +41410,7 @@
         <v>-0.162378931418392</v>
       </c>
       <c r="E14" s="8" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
     </row>
   </sheetData>
@@ -41175,21 +41438,21 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="0" t="s">
-        <v>682</v>
+        <v>685</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="5" t="s">
-        <v>683</v>
+        <v>686</v>
       </c>
       <c r="B3" s="15" t="s">
-        <v>684</v>
+        <v>687</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>685</v>
+        <v>688</v>
       </c>
       <c r="D3" s="15" t="s">
-        <v>686</v>
+        <v>689</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -41211,7 +41474,7 @@
     </row>
     <row r="5" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="s">
-        <v>687</v>
+        <v>690</v>
       </c>
       <c r="B5" s="18" t="n">
         <f aca="false">(PL!C7-0.3*u_rb_27*ct_VR*(1+px27)*(1+ai_oth))*(gm27_A-opex)*ni_op*fx/shares</f>
@@ -41228,7 +41491,7 @@
     </row>
     <row r="6" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="s">
-        <v>688</v>
+        <v>691</v>
       </c>
       <c r="B6" s="18" t="n">
         <f aca="false">(PL!C7-PL!C5*px27/(1+px27))*(gm27_A-opex)*ni_op*fx/shares</f>
@@ -41245,7 +41508,7 @@
     </row>
     <row r="7" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="4" t="s">
-        <v>689</v>
+        <v>692</v>
       </c>
       <c r="B7" s="18" t="n">
         <f aca="false">(PL!C7)*(0.6-opex)*ni_op*fx/shares</f>
@@ -41262,7 +41525,7 @@
     </row>
     <row r="8" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="4" t="s">
-        <v>690</v>
+        <v>693</v>
       </c>
       <c r="B8" s="18" t="n">
         <f aca="false">(PL!C7)*(0.67-opex)*ni_op*fx/shares</f>
@@ -41279,7 +41542,7 @@
     </row>
     <row r="9" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="4" t="s">
-        <v>691</v>
+        <v>694</v>
       </c>
       <c r="B9" s="18" t="n">
         <f aca="false">(PL!C7-PL!B6*na27_A)*(gm27_A-opex)*ni_op*fx/shares</f>
@@ -41296,7 +41559,7 @@
     </row>
     <row r="10" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="0" t="s">
-        <v>692</v>
+        <v>695</v>
       </c>
       <c r="B10" s="18" t="n">
         <f aca="false">(PL!C7)*(gm27_A-opex)*ni_op*fx/shares</f>
@@ -41313,32 +41576,32 @@
     </row>
     <row r="13" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
-        <v>693</v>
+        <v>696</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="5" t="s">
-        <v>694</v>
+        <v>697</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>695</v>
+        <v>698</v>
       </c>
       <c r="C14" s="15" t="s">
-        <v>684</v>
+        <v>687</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>685</v>
+        <v>688</v>
       </c>
       <c r="E14" s="15" t="s">
-        <v>696</v>
+        <v>699</v>
       </c>
       <c r="F14" s="5" t="s">
-        <v>685</v>
+        <v>688</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="4" t="s">
-        <v>697</v>
+        <v>700</v>
       </c>
       <c r="B15" s="9" t="n">
         <f aca="false">ni_op</f>
@@ -41363,7 +41626,7 @@
     </row>
     <row r="16" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="4" t="s">
-        <v>698</v>
+        <v>701</v>
       </c>
       <c r="B16" s="9" t="n">
         <f aca="false">ni_op_lo</f>
@@ -41388,7 +41651,7 @@
     </row>
     <row r="17" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="4" t="s">
-        <v>699</v>
+        <v>702</v>
       </c>
       <c r="B17" s="9" t="n">
         <f aca="false">ni_op_hi</f>
@@ -41413,27 +41676,27 @@
     </row>
     <row r="21" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="s">
-        <v>700</v>
+        <v>703</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="5" t="s">
-        <v>701</v>
+        <v>704</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>694</v>
+        <v>697</v>
       </c>
       <c r="C22" s="15" t="s">
-        <v>702</v>
+        <v>705</v>
       </c>
       <c r="D22" s="15" t="s">
-        <v>703</v>
+        <v>706</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>704</v>
+        <v>707</v>
       </c>
       <c r="F22" s="5" t="s">
-        <v>685</v>
+        <v>688</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -41441,7 +41704,7 @@
         <v>25</v>
       </c>
       <c r="B23" s="0" t="s">
-        <v>705</v>
+        <v>708</v>
       </c>
       <c r="C23" s="16" t="n">
         <f aca="false">(tp_wA*(Val!B63*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^1+Val!B64*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^2+Val!B65*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^3+Val!B66*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^4+Val!B67*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^5+Val!B68*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^6+Val!B68*(1-MIN(tp_g/tp_roe,0.8))*(1+tp_g)/(tp_r-tp_g)/(1+tp_r)^6)+tp_wB*(Val!C63*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^1+Val!C64*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^2+Val!C65*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^3+Val!C66*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^4+Val!C67*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^5+Val!C68*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^6+Val!C68*(1-MIN(tp_g/tp_roe,0.8))*(1+tp_g)/(tp_r-tp_g)/(1+tp_r)^6)+tp_wC*(Val!D63*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^1+Val!D64*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^2+Val!D65*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^3+Val!D66*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^4+Val!D67*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^5+Val!D68*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^6+Val!D68*(1-MIN(tp_g/tp_roe,0.8))*(1+tp_g)/(tp_r-tp_g)/(1+tp_r)^6))*(1+tp_r)</f>
@@ -41462,10 +41725,10 @@
     </row>
     <row r="24" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="4" t="s">
-        <v>706</v>
+        <v>709</v>
       </c>
       <c r="B24" s="0" t="s">
-        <v>707</v>
+        <v>710</v>
       </c>
       <c r="C24" s="16" t="n">
         <f aca="false">(tp_wA*(Val!B63*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r+0.01))^1+Val!B64*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r+0.01))^2+Val!B65*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r+0.01))^3+Val!B66*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r+0.01))^4+Val!B67*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r+0.01))^5+Val!B68*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r+0.01))^6+Val!B68*(1-MIN(tp_g/tp_roe,0.8))*(1+tp_g)/((tp_r+0.01)-tp_g)/(1+(tp_r+0.01))^6)+tp_wB*(Val!C63*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r+0.01))^1+Val!C64*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r+0.01))^2+Val!C65*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r+0.01))^3+Val!C66*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r+0.01))^4+Val!C67*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r+0.01))^5+Val!C68*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r+0.01))^6+Val!C68*(1-MIN(tp_g/tp_roe,0.8))*(1+tp_g)/((tp_r+0.01)-tp_g)/(1+(tp_r+0.01))^6)+tp_wC*(Val!D63*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r+0.01))^1+Val!D64*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r+0.01))^2+Val!D65*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r+0.01))^3+Val!D66*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r+0.01))^4+Val!D67*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r+0.01))^5+Val!D68*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r+0.01))^6+Val!D68*(1-MIN(tp_g/tp_roe,0.8))*(1+tp_g)/((tp_r+0.01)-tp_g)/(1+(tp_r+0.01))^6))*(1+(tp_r+0.01))</f>
@@ -41486,10 +41749,10 @@
     </row>
     <row r="25" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="4" t="s">
-        <v>708</v>
+        <v>711</v>
       </c>
       <c r="B25" s="0" t="s">
-        <v>709</v>
+        <v>712</v>
       </c>
       <c r="C25" s="16" t="n">
         <f aca="false">(tp_wA*(Val!B63*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r-0.01))^1+Val!B64*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r-0.01))^2+Val!B65*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r-0.01))^3+Val!B66*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r-0.01))^4+Val!B67*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r-0.01))^5+Val!B68*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r-0.01))^6+Val!B68*(1-MIN(tp_g/tp_roe,0.8))*(1+tp_g)/((tp_r-0.01)-tp_g)/(1+(tp_r-0.01))^6)+tp_wB*(Val!C63*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r-0.01))^1+Val!C64*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r-0.01))^2+Val!C65*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r-0.01))^3+Val!C66*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r-0.01))^4+Val!C67*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r-0.01))^5+Val!C68*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r-0.01))^6+Val!C68*(1-MIN(tp_g/tp_roe,0.8))*(1+tp_g)/((tp_r-0.01)-tp_g)/(1+(tp_r-0.01))^6)+tp_wC*(Val!D63*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r-0.01))^1+Val!D64*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r-0.01))^2+Val!D65*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r-0.01))^3+Val!D66*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r-0.01))^4+Val!D67*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r-0.01))^5+Val!D68*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r-0.01))^6+Val!D68*(1-MIN(tp_g/tp_roe,0.8))*(1+tp_g)/((tp_r-0.01)-tp_g)/(1+(tp_r-0.01))^6))*(1+(tp_r-0.01))</f>
@@ -41510,10 +41773,10 @@
     </row>
     <row r="26" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="4" t="s">
-        <v>710</v>
+        <v>713</v>
       </c>
       <c r="B26" s="0" t="s">
-        <v>711</v>
+        <v>714</v>
       </c>
       <c r="C26" s="16" t="n">
         <f aca="false">(tp_wA*(Val!B63*(1-MIN((tp_g+0.01)/tp_roe,0.8))/(1+tp_r)^1+Val!B64*(1-MIN((tp_g+0.01)/tp_roe,0.8))/(1+tp_r)^2+Val!B65*(1-MIN((tp_g+0.01)/tp_roe,0.8))/(1+tp_r)^3+Val!B66*(1-MIN((tp_g+0.01)/tp_roe,0.8))/(1+tp_r)^4+Val!B67*(1-MIN((tp_g+0.01)/tp_roe,0.8))/(1+tp_r)^5+Val!B68*(1-MIN((tp_g+0.01)/tp_roe,0.8))/(1+tp_r)^6+Val!B68*(1-MIN((tp_g+0.01)/tp_roe,0.8))*(1+(tp_g+0.01))/(tp_r-(tp_g+0.01))/(1+tp_r)^6)+tp_wB*(Val!C63*(1-MIN((tp_g+0.01)/tp_roe,0.8))/(1+tp_r)^1+Val!C64*(1-MIN((tp_g+0.01)/tp_roe,0.8))/(1+tp_r)^2+Val!C65*(1-MIN((tp_g+0.01)/tp_roe,0.8))/(1+tp_r)^3+Val!C66*(1-MIN((tp_g+0.01)/tp_roe,0.8))/(1+tp_r)^4+Val!C67*(1-MIN((tp_g+0.01)/tp_roe,0.8))/(1+tp_r)^5+Val!C68*(1-MIN((tp_g+0.01)/tp_roe,0.8))/(1+tp_r)^6+Val!C68*(1-MIN((tp_g+0.01)/tp_roe,0.8))*(1+(tp_g+0.01))/(tp_r-(tp_g+0.01))/(1+tp_r)^6)+tp_wC*(Val!D63*(1-MIN((tp_g+0.01)/tp_roe,0.8))/(1+tp_r)^1+Val!D64*(1-MIN((tp_g+0.01)/tp_roe,0.8))/(1+tp_r)^2+Val!D65*(1-MIN((tp_g+0.01)/tp_roe,0.8))/(1+tp_r)^3+Val!D66*(1-MIN((tp_g+0.01)/tp_roe,0.8))/(1+tp_r)^4+Val!D67*(1-MIN((tp_g+0.01)/tp_roe,0.8))/(1+tp_r)^5+Val!D68*(1-MIN((tp_g+0.01)/tp_roe,0.8))/(1+tp_r)^6+Val!D68*(1-MIN((tp_g+0.01)/tp_roe,0.8))*(1+(tp_g+0.01))/(tp_r-(tp_g+0.01))/(1+tp_r)^6))*(1+tp_r)</f>
@@ -41534,10 +41797,10 @@
     </row>
     <row r="27" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="4" t="s">
-        <v>712</v>
+        <v>715</v>
       </c>
       <c r="B27" s="0" t="s">
-        <v>713</v>
+        <v>716</v>
       </c>
       <c r="C27" s="16" t="n">
         <f aca="false">(tp_wA*(Val!B63*(1-MIN((tp_g-0.01)/tp_roe,0.8))/(1+tp_r)^1+Val!B64*(1-MIN((tp_g-0.01)/tp_roe,0.8))/(1+tp_r)^2+Val!B65*(1-MIN((tp_g-0.01)/tp_roe,0.8))/(1+tp_r)^3+Val!B66*(1-MIN((tp_g-0.01)/tp_roe,0.8))/(1+tp_r)^4+Val!B67*(1-MIN((tp_g-0.01)/tp_roe,0.8))/(1+tp_r)^5+Val!B68*(1-MIN((tp_g-0.01)/tp_roe,0.8))/(1+tp_r)^6+Val!B68*(1-MIN((tp_g-0.01)/tp_roe,0.8))*(1+(tp_g-0.01))/(tp_r-(tp_g-0.01))/(1+tp_r)^6)+tp_wB*(Val!C63*(1-MIN((tp_g-0.01)/tp_roe,0.8))/(1+tp_r)^1+Val!C64*(1-MIN((tp_g-0.01)/tp_roe,0.8))/(1+tp_r)^2+Val!C65*(1-MIN((tp_g-0.01)/tp_roe,0.8))/(1+tp_r)^3+Val!C66*(1-MIN((tp_g-0.01)/tp_roe,0.8))/(1+tp_r)^4+Val!C67*(1-MIN((tp_g-0.01)/tp_roe,0.8))/(1+tp_r)^5+Val!C68*(1-MIN((tp_g-0.01)/tp_roe,0.8))/(1+tp_r)^6+Val!C68*(1-MIN((tp_g-0.01)/tp_roe,0.8))*(1+(tp_g-0.01))/(tp_r-(tp_g-0.01))/(1+tp_r)^6)+tp_wC*(Val!D63*(1-MIN((tp_g-0.01)/tp_roe,0.8))/(1+tp_r)^1+Val!D64*(1-MIN((tp_g-0.01)/tp_roe,0.8))/(1+tp_r)^2+Val!D65*(1-MIN((tp_g-0.01)/tp_roe,0.8))/(1+tp_r)^3+Val!D66*(1-MIN((tp_g-0.01)/tp_roe,0.8))/(1+tp_r)^4+Val!D67*(1-MIN((tp_g-0.01)/tp_roe,0.8))/(1+tp_r)^5+Val!D68*(1-MIN((tp_g-0.01)/tp_roe,0.8))/(1+tp_r)^6+Val!D68*(1-MIN((tp_g-0.01)/tp_roe,0.8))*(1+(tp_g-0.01))/(tp_r-(tp_g-0.01))/(1+tp_r)^6))*(1+tp_r)</f>
@@ -41558,10 +41821,10 @@
     </row>
     <row r="28" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="0" t="s">
-        <v>714</v>
+        <v>717</v>
       </c>
       <c r="B28" s="0" t="s">
-        <v>715</v>
+        <v>718</v>
       </c>
       <c r="C28" s="16" t="n">
         <f aca="false">(tp_wA*(Val!B63*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^1+Val!B64*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^2+Val!B65*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^3+Val!B66*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^4+Val!B67*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^5+Val!B68*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^6+Val!B68*(1-MIN(tp_g/tp_roe,0.8))*(1+tp_g)/(tp_r-tp_g)/(1+tp_r)^6)+tp_wB*(Val!C63*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^1+Val!C64*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^2+Val!C65*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^3+Val!C66*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^4+Val!C67*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^5+Val!C68*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^6+Val!C68*(1-MIN(tp_g/tp_roe,0.8))*(1+tp_g)/(tp_r-tp_g)/(1+tp_r)^6)+tp_wC*(Val!D63*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^1+Val!D64*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^2+Val!D65*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^3+Val!D66*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^4+Val!D67*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^5+Val!D68*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^6+Val!D68*(1-MIN(tp_g/tp_roe,0.8))*(1+tp_g)/(tp_r-tp_g)/(1+tp_r)^6))*(1+tp_r)</f>
@@ -41582,10 +41845,10 @@
     </row>
     <row r="29" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="0" t="s">
-        <v>716</v>
+        <v>719</v>
       </c>
       <c r="B29" s="0" t="s">
-        <v>717</v>
+        <v>720</v>
       </c>
       <c r="C29" s="16" t="n">
         <f aca="false">(tp_wA*(Val!B63*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^1+Val!B64*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^2+Val!B65*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^3+Val!B66*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^4+Val!B67*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^5+Val!B68*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^6+Val!B68*(1-MIN(tp_g/tp_roe,0.8))*(1+tp_g)/(tp_r-tp_g)/(1+tp_r)^6)+tp_wB*(Val!C63*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^1+Val!C64*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^2+Val!C65*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^3+Val!C66*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^4+Val!C67*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^5+Val!C68*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^6+Val!C68*(1-MIN(tp_g/tp_roe,0.8))*(1+tp_g)/(tp_r-tp_g)/(1+tp_r)^6)+tp_wC*(Val!D63*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^1+Val!D64*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^2+Val!D65*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^3+Val!D66*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^4+Val!D67*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^5+Val!D68*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^6+Val!D68*(1-MIN(tp_g/tp_roe,0.8))*(1+tp_g)/(tp_r-tp_g)/(1+tp_r)^6))*(1+tp_r)</f>
@@ -41606,7 +41869,7 @@
     </row>
     <row r="30" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="4" t="s">
-        <v>718</v>
+        <v>721</v>
       </c>
       <c r="C30" s="29" t="n">
         <f aca="false">C23-Val!B79</f>
@@ -41640,51 +41903,51 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="0" t="s">
-        <v>719</v>
+        <v>722</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="5" t="s">
-        <v>720</v>
+        <v>723</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>508</v>
+        <v>511</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>721</v>
+        <v>724</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>722</v>
+        <v>725</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>723</v>
+        <v>726</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>509</v>
+        <v>512</v>
       </c>
       <c r="G3" s="5" t="s">
-        <v>724</v>
+        <v>727</v>
       </c>
       <c r="H3" s="5" t="s">
-        <v>725</v>
+        <v>728</v>
       </c>
       <c r="I3" s="5" t="s">
-        <v>726</v>
+        <v>729</v>
       </c>
       <c r="J3" s="5" t="s">
-        <v>727</v>
+        <v>730</v>
       </c>
       <c r="K3" s="5" t="s">
-        <v>728</v>
+        <v>731</v>
       </c>
       <c r="L3" s="5" t="s">
-        <v>729</v>
+        <v>732</v>
       </c>
       <c r="M3" s="5" t="s">
-        <v>730</v>
+        <v>733</v>
       </c>
       <c r="N3" s="5" t="s">
-        <v>731</v>
+        <v>734</v>
       </c>
       <c r="O3" s="5" t="s">
         <v>27</v>
@@ -41695,7 +41958,7 @@
     </row>
     <row r="4" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="0" t="s">
-        <v>547</v>
+        <v>550</v>
       </c>
       <c r="B4" s="30" t="n">
         <v>1121.28</v>
@@ -41739,15 +42002,15 @@
         <v>1</v>
       </c>
       <c r="O4" s="8" t="s">
-        <v>732</v>
+        <v>735</v>
       </c>
       <c r="P4" s="4" t="s">
-        <v>733</v>
+        <v>736</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="s">
-        <v>548</v>
+        <v>551</v>
       </c>
       <c r="B5" s="30" t="n">
         <v>921.47</v>
@@ -41792,15 +42055,15 @@
         <v>2</v>
       </c>
       <c r="O5" s="8" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="P5" s="4" t="s">
-        <v>734</v>
+        <v>737</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="s">
-        <v>549</v>
+        <v>552</v>
       </c>
       <c r="B6" s="30" t="n">
         <v>1322.05</v>
@@ -41847,15 +42110,15 @@
         <v>2</v>
       </c>
       <c r="O6" s="8" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="P6" s="4" t="s">
-        <v>735</v>
+        <v>738</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="0" t="s">
-        <v>550</v>
+        <v>553</v>
       </c>
       <c r="B7" s="30" t="n">
         <v>1936.09</v>
@@ -41902,15 +42165,15 @@
         <v>2</v>
       </c>
       <c r="O7" s="8" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="P7" s="4" t="s">
-        <v>736</v>
+        <v>739</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="0" t="s">
-        <v>737</v>
+        <v>740</v>
       </c>
       <c r="B8" s="25" t="n">
         <f aca="false">ntd26_1q*opm26_1q</f>
@@ -41958,12 +42221,12 @@
         <v>128</v>
       </c>
       <c r="P8" s="4" t="s">
-        <v>738</v>
+        <v>741</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="0" t="s">
-        <v>739</v>
+        <v>742</v>
       </c>
       <c r="B9" s="25" t="n">
         <f aca="false">ntd26_2q*opm26_2q</f>
@@ -42007,15 +42270,15 @@
         <v>2</v>
       </c>
       <c r="O9" s="8" t="s">
-        <v>740</v>
+        <v>743</v>
       </c>
       <c r="P9" s="4" t="s">
-        <v>741</v>
+        <v>744</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="0" t="s">
-        <v>742</v>
+        <v>745</v>
       </c>
       <c r="B10" s="30" t="n">
         <v>876.45</v>
@@ -42058,15 +42321,15 @@
         <v>2</v>
       </c>
       <c r="O10" s="8" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="P10" s="4" t="s">
-        <v>743</v>
+        <v>746</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="0" t="s">
-        <v>744</v>
+        <v>747</v>
       </c>
       <c r="B11" s="25" t="n">
         <f aca="false">SUM(B8:B10)</f>
@@ -42114,53 +42377,53 @@
         <v>128</v>
       </c>
       <c r="P11" s="4" t="s">
-        <v>745</v>
+        <v>748</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
-        <v>746</v>
+        <v>749</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="4" t="s">
-        <v>747</v>
+        <v>750</v>
       </c>
       <c r="B14" s="14" t="n">
         <f aca="false">(E6+E7+E11)/(D6+D7+D11)</f>
         <v>0.165580350953154</v>
       </c>
       <c r="P14" s="4" t="s">
-        <v>748</v>
+        <v>751</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="4" t="s">
-        <v>749</v>
+        <v>752</v>
       </c>
       <c r="B15" s="14" t="n">
         <f aca="false">(SUM(C4:C7)+C11-I11)/(SUM(B4:B7)+B11)</f>
         <v>0.0481460113069807</v>
       </c>
       <c r="P15" s="4" t="s">
-        <v>750</v>
+        <v>753</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="4" t="s">
-        <v>751</v>
+        <v>754</v>
       </c>
       <c r="B16" s="9" t="n">
         <f aca="false">(1+B15)*(1-B14)</f>
         <v>0.874593626904623</v>
       </c>
       <c r="P16" s="4" t="s">
-        <v>752</v>
+        <v>755</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="4" t="s">
-        <v>753</v>
+        <v>756</v>
       </c>
       <c r="B17" s="9" t="n">
         <f aca="false">(F6+F7)/(B6+B7)</f>
@@ -42169,72 +42432,72 @@
     </row>
     <row r="18" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="4" t="s">
-        <v>754</v>
+        <v>757</v>
       </c>
       <c r="B18" s="9" t="n">
         <f aca="false">M11</f>
         <v>0.887328973543092</v>
       </c>
       <c r="P18" s="4" t="s">
-        <v>755</v>
+        <v>758</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="4" t="s">
-        <v>756</v>
+        <v>759</v>
       </c>
       <c r="B19" s="9" t="n">
         <f aca="false">(F11-I11*(1-B14))/B11</f>
         <v>0.864414533026079</v>
       </c>
       <c r="P19" s="8" t="s">
-        <v>757</v>
+        <v>760</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="4" t="s">
-        <v>758</v>
+        <v>761</v>
       </c>
       <c r="B20" s="9" t="n">
         <f aca="false">M5</f>
         <v>0.909166874667651</v>
       </c>
       <c r="P20" s="8" t="s">
-        <v>759</v>
+        <v>762</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="4" t="s">
-        <v>760</v>
+        <v>763</v>
       </c>
       <c r="B21" s="14" t="n">
         <f aca="false">(SUM(C4:C7)+C11)/(SUM(B4:B7)+B11)</f>
         <v>0.0564592945007984</v>
       </c>
       <c r="P21" s="4" t="s">
-        <v>761</v>
+        <v>764</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="4" t="s">
-        <v>762</v>
+        <v>765</v>
       </c>
       <c r="B22" s="9" t="n">
         <f aca="false">(1+B21)*(1-B14)</f>
         <v>0.881530393749635</v>
       </c>
       <c r="P22" s="4" t="s">
-        <v>763</v>
+        <v>766</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="4" t="s">
-        <v>764</v>
+        <v>767</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="4" t="s">
-        <v>765</v>
+        <v>768</v>
       </c>
     </row>
   </sheetData>
@@ -42262,332 +42525,332 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>603</v>
+        <v>606</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="4" t="s">
-        <v>766</v>
+        <v>769</v>
       </c>
       <c r="B2" s="0" t="s">
-        <v>767</v>
+        <v>770</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="4" t="s">
-        <v>768</v>
+        <v>771</v>
       </c>
       <c r="B3" s="0" t="s">
-        <v>769</v>
+        <v>772</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
-        <v>770</v>
+        <v>773</v>
       </c>
       <c r="B4" s="0" t="s">
-        <v>771</v>
+        <v>774</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="4" t="s">
-        <v>772</v>
+        <v>775</v>
       </c>
       <c r="B5" s="0" t="s">
-        <v>773</v>
+        <v>776</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="s">
-        <v>774</v>
+        <v>777</v>
       </c>
       <c r="B6" s="0" t="s">
-        <v>775</v>
+        <v>778</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="0" t="s">
-        <v>776</v>
+        <v>779</v>
       </c>
       <c r="B7" s="0" t="s">
-        <v>777</v>
+        <v>780</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="4" t="s">
-        <v>778</v>
+        <v>781</v>
       </c>
       <c r="B8" s="0" t="s">
-        <v>779</v>
+        <v>782</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="0" t="s">
-        <v>780</v>
+        <v>783</v>
       </c>
       <c r="B9" s="0" t="s">
-        <v>781</v>
+        <v>784</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="4" t="s">
-        <v>782</v>
+        <v>785</v>
       </c>
       <c r="B10" s="0" t="s">
-        <v>783</v>
+        <v>786</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="0" t="s">
-        <v>784</v>
+        <v>787</v>
       </c>
       <c r="B11" s="0" t="s">
-        <v>785</v>
+        <v>788</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="0" t="s">
-        <v>786</v>
+        <v>789</v>
       </c>
       <c r="B12" s="0" t="s">
-        <v>787</v>
+        <v>790</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="0" t="s">
-        <v>788</v>
+        <v>791</v>
       </c>
       <c r="B13" s="0" t="s">
-        <v>789</v>
+        <v>792</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="4" t="s">
-        <v>790</v>
+        <v>793</v>
       </c>
       <c r="B14" s="0" t="s">
-        <v>791</v>
+        <v>794</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="4" t="s">
-        <v>792</v>
+        <v>795</v>
       </c>
       <c r="B15" s="0" t="s">
-        <v>793</v>
+        <v>796</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="4" t="s">
-        <v>794</v>
+        <v>797</v>
       </c>
       <c r="B16" s="0" t="s">
-        <v>795</v>
+        <v>798</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="4" t="s">
-        <v>796</v>
+        <v>799</v>
       </c>
       <c r="B17" s="0" t="s">
-        <v>797</v>
+        <v>800</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="4" t="s">
-        <v>798</v>
+        <v>801</v>
       </c>
       <c r="B18" s="0" t="s">
-        <v>799</v>
+        <v>802</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="4" t="s">
-        <v>800</v>
+        <v>803</v>
       </c>
       <c r="B19" s="0" t="s">
-        <v>801</v>
+        <v>804</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="4" t="s">
-        <v>802</v>
+        <v>805</v>
       </c>
       <c r="B20" s="0" t="s">
-        <v>803</v>
+        <v>806</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="4" t="s">
-        <v>804</v>
+        <v>807</v>
       </c>
       <c r="B21" s="0" t="s">
-        <v>805</v>
+        <v>808</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="4" t="s">
-        <v>806</v>
+        <v>809</v>
       </c>
       <c r="B22" s="0" t="s">
-        <v>807</v>
+        <v>810</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="4" t="s">
-        <v>808</v>
+        <v>811</v>
       </c>
       <c r="B23" s="0" t="s">
-        <v>809</v>
+        <v>812</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="4" t="s">
-        <v>810</v>
+        <v>813</v>
       </c>
       <c r="B24" s="0" t="s">
-        <v>811</v>
+        <v>814</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="4" t="s">
-        <v>812</v>
+        <v>815</v>
       </c>
       <c r="B25" s="0" t="s">
-        <v>813</v>
+        <v>816</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="4" t="s">
-        <v>814</v>
+        <v>817</v>
       </c>
       <c r="B26" s="0" t="s">
-        <v>815</v>
+        <v>818</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="4" t="s">
-        <v>816</v>
+        <v>819</v>
       </c>
       <c r="B27" s="0" t="s">
-        <v>817</v>
+        <v>820</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="4" t="s">
-        <v>818</v>
+        <v>821</v>
       </c>
       <c r="B28" s="0" t="s">
-        <v>819</v>
+        <v>822</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="4" t="s">
-        <v>820</v>
+        <v>823</v>
       </c>
       <c r="B29" s="0" t="s">
-        <v>821</v>
+        <v>824</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="4" t="s">
-        <v>822</v>
+        <v>825</v>
       </c>
       <c r="B30" s="0" t="s">
-        <v>823</v>
+        <v>826</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="4" t="s">
-        <v>824</v>
+        <v>827</v>
       </c>
       <c r="B31" s="0" t="s">
-        <v>825</v>
+        <v>828</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="4" t="s">
-        <v>826</v>
+        <v>829</v>
       </c>
       <c r="B32" s="0" t="s">
-        <v>827</v>
+        <v>830</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="4" t="s">
-        <v>828</v>
+        <v>831</v>
       </c>
       <c r="B33" s="0" t="s">
-        <v>829</v>
+        <v>832</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="4" t="s">
-        <v>830</v>
+        <v>833</v>
       </c>
       <c r="B34" s="0" t="s">
-        <v>795</v>
+        <v>798</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="4" t="s">
-        <v>831</v>
+        <v>834</v>
       </c>
       <c r="B35" s="0" t="s">
-        <v>832</v>
+        <v>835</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="4" t="s">
-        <v>833</v>
+        <v>836</v>
       </c>
       <c r="B36" s="0" t="s">
-        <v>834</v>
+        <v>837</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="4" t="s">
-        <v>835</v>
+        <v>838</v>
       </c>
       <c r="B37" s="0" t="s">
-        <v>836</v>
+        <v>839</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="4" t="s">
-        <v>837</v>
+        <v>840</v>
       </c>
       <c r="B38" s="0" t="s">
-        <v>838</v>
+        <v>841</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="4" t="s">
-        <v>839</v>
+        <v>842</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>840</v>
+        <v>843</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="0" t="s">
-        <v>841</v>
+        <v>844</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="0" t="s">
-        <v>842</v>
+        <v>845</v>
       </c>
       <c r="B41" s="0" t="s">
-        <v>843</v>
+        <v>846</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="0" t="s">
-        <v>844</v>
+        <v>847</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>845</v>
+        <v>848</v>
       </c>
     </row>
   </sheetData>
